--- a/results/05_transient_transcription_output/501/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/501/Top_Excel_with_OCR_Results.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5698
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
@@ -656,7 +656,7 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -668,7 +668,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -683,25 +683,25 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">43
+</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2468
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
@@ -724,7 +724,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -736,13 +736,13 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
@@ -760,7 +760,9 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>08561435132</t>
+          <t xml:space="preserve">27
+2
+</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -771,7 +773,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -783,11 +785,15 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">84
@@ -814,13 +820,13 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">355
 </t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -838,7 +844,7 @@
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -850,7 +856,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
@@ -862,7 +868,7 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">088
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
@@ -886,14 +892,13 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>808</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -911,7 +916,7 @@
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">339
+          <t xml:space="preserve">3321
 </t>
         </is>
       </c>
@@ -921,10 +926,15 @@
 </t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2319
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -942,7 +952,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -954,31 +964,30 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>94887</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
+          <t xml:space="preserve">408
 </t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -996,7 +1005,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -1020,12 +1029,13 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -1049,18 +1059,18 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5836
+          <t xml:space="preserve">536
 </t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>352</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1078,7 +1088,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1096,7 +1106,8 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,13 +1124,13 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -1131,7 +1142,7 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">347
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -1173,13 +1184,13 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1203,36 +1214,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>425</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">344
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">034
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
@@ -1240,31 +1247,32 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">022
 </t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">365
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1287,7 +1295,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -1305,18 +1313,17 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>15</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -1344,27 +1351,38 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660
-</t>
+          <t>26562</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>611</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
+          <t xml:space="preserve">533
+</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1114
+</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2262
+411464141
+</t>
+        </is>
+      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">442
@@ -1379,26 +1397,26 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">671
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1838
+          <t xml:space="preserve">1830
 </t>
         </is>
       </c>
@@ -1410,13 +1428,13 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650
+          <t xml:space="preserve">16850
 </t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -1429,7 +1447,7 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2241
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
@@ -1441,25 +1459,25 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">389
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1062
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
@@ -1477,17 +1495,19 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1516,39 +1536,35 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>326</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366
-</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t xml:space="preserve">366
+</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">330
@@ -1563,48 +1579,48 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>55</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">448
+</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1382
+</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1841
+</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">448
-</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="Y10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1502
 </t>
         </is>
       </c>
@@ -1622,13 +1638,13 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4279
+          <t xml:space="preserve">4229
 </t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -1645,24 +1661,23 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>411</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
@@ -1681,17 +1696,18 @@
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2
+8
 </t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1710,13 +1726,13 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">2290
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -1728,19 +1744,19 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1023
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
+          <t xml:space="preserve">4240
 </t>
         </is>
       </c>
@@ -1759,19 +1775,19 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 6
+          <t xml:space="preserve">567
 </t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 317
+          <t xml:space="preserve">7119
 </t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1783,13 +1799,14 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">148
+</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1806,7 +1823,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -1824,7 +1841,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -1842,18 +1859,18 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3108
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -1865,35 +1882,32 @@
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>048</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="n"/>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">45
+76
 </t>
         </is>
       </c>
@@ -1911,7 +1925,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6013
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
@@ -1923,7 +1937,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -1941,7 +1955,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -1977,7 +1991,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -1989,7 +2003,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">396
 </t>
         </is>
       </c>
@@ -2001,7 +2015,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2019,20 +2033,19 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">440
+          <t xml:space="preserve">496
 </t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">2872
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
@@ -2043,7 +2056,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">408
 </t>
         </is>
       </c>
@@ -2074,7 +2087,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -2092,7 +2105,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -2110,13 +2123,13 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">020
 </t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -2128,13 +2141,13 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -2146,19 +2159,19 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3803
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -2170,20 +2183,18 @@
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>412</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
@@ -2221,19 +2232,18 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1795
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -2256,7 +2266,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2268,13 +2278,13 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2298,13 +2308,13 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -2322,7 +2332,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -2346,7 +2356,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
@@ -2364,25 +2374,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95721
+          <t xml:space="preserve">25777
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11896
+          <t xml:space="preserve">526
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>81</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2399,49 +2408,56 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">353
+</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">362
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">1811
+14
 </t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
+          <t xml:space="preserve">8223
 </t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t xml:space="preserve">443222
+181909191
+</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125
+          <t xml:space="preserve">21215
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">622
 </t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1547
+          <t xml:space="preserve">547
 </t>
         </is>
       </c>
@@ -2458,11 +2474,17 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr"/>
+          <t xml:space="preserve">8206
+</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+7918949
+</t>
+        </is>
+      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1315
@@ -2471,7 +2493,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2483,13 +2505,13 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1458
+          <t xml:space="preserve">1488
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -2507,25 +2529,25 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2537,41 +2559,41 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1134
+</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">425
@@ -2580,63 +2602,65 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">0624
 </t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">3609
 </t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t xml:space="preserve">263
+</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">7
+</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">849
+          <t xml:space="preserve">449
 </t>
         </is>
       </c>
@@ -2654,50 +2678,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521
+          <t xml:space="preserve">521
+2
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>349</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 7
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">80
+</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">135
@@ -2706,30 +2727,30 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
@@ -2740,19 +2761,18 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">376
+          <t xml:space="preserve">3726
 </t>
         </is>
       </c>
@@ -2782,7 +2802,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -2800,17 +2820,23 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264
+          <t xml:space="preserve">268
+2975
 </t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">229
@@ -2825,7 +2851,8 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2841,7 +2868,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2856,15 +2883,10 @@
           <t>26</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
+      <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
+          <t xml:space="preserve">608
 </t>
         </is>
       </c>
@@ -2876,12 +2898,13 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t xml:space="preserve">320
+</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -2899,34 +2922,33 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>962</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>61</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="Z19" s="2" t="n"/>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
           <t>12</t>
@@ -2939,13 +2961,15 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5429
-</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">446466240
+212
+79719019
+</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">123
@@ -2954,8 +2978,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2972,7 +2995,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -2984,7 +3007,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2996,19 +3019,19 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -3020,13 +3043,13 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>106</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -3043,23 +3066,27 @@
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">414
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
-        </is>
-      </c>
-      <c r="X20" s="2" t="inlineStr"/>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">320
@@ -3079,11 +3106,21 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5422
+</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">309
+</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -3094,90 +3131,89 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1231
+</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63
+</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1256
+</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">307
+</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4920
-</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">122
+</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -3195,7 +3231,8 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -3206,7 +3243,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>146</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3223,12 +3260,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>341</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3239,14 +3276,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>435</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -3257,19 +3292,20 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">200
+</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -3280,19 +3316,19 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3303,7 +3339,7 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -3320,7 +3356,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -3332,7 +3368,8 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t xml:space="preserve">220
+</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3343,7 +3380,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -3366,36 +3403,38 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25475
-</t>
-        </is>
-      </c>
+      <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">603
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
+          <t xml:space="preserve">868
+</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44255
+82947
+</t>
+        </is>
+      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">361
@@ -3404,11 +3443,15 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr"/>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
           <t>22</t>
@@ -3416,35 +3459,35 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2720
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>736</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -3455,19 +3498,18 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">2920
 </t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -3485,11 +3527,16 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="2" t="n"/>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1921
+</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3504,7 +3551,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>50321</t>
+          <t>50261</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3515,30 +3562,31 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1784
 </t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -3550,48 +3598,46 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">546
 </t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t xml:space="preserve">83
+</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1544
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -3614,7 +3660,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -3632,13 +3678,14 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t xml:space="preserve">225
+</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3655,42 +3702,51 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">4555
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
@@ -3700,14 +3756,19 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
+          <t xml:space="preserve">4008
 </t>
         </is>
       </c>
@@ -3719,13 +3780,13 @@
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t xml:space="preserve">5
+</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3735,16 +3796,23 @@
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr"/>
-      <c r="U25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+2
+</t>
+        </is>
+      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 6 11558
+          <t xml:space="preserve">182
+171111
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3756,8 +3824,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">455
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Z25" s="2" t="n"/>
@@ -3787,37 +3854,37 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2448
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">1089
 </t>
         </is>
       </c>
@@ -3829,19 +3896,19 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">020
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
@@ -3865,7 +3932,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3877,28 +3944,30 @@
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>328234</t>
+          <t xml:space="preserve">8
+</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">2664
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">1494
+</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -3917,52 +3986,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5501
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820
+          <t xml:space="preserve">22858
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16816
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">163
@@ -3977,19 +4051,19 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13220
+          <t xml:space="preserve">5280
 </t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -4007,7 +4081,7 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -4019,34 +4093,36 @@
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>42</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>266</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">262
+309
 </t>
         </is>
       </c>
@@ -4070,7 +4146,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>334</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -4081,7 +4157,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -4093,25 +4169,25 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -4123,25 +4199,25 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
+          <t xml:space="preserve">4280
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -4153,43 +4229,47 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="n"/>
+          <t xml:space="preserve">1660
+</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>132</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="Z28" s="2" t="n"/>
@@ -4207,20 +4287,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6249
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -4237,12 +4314,13 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">204
+</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -4253,7 +4331,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -4271,13 +4349,13 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
@@ -4295,18 +4373,22 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
-</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr"/>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr"/>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="n"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">277
@@ -4347,7 +4429,7 @@
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15616
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
@@ -4359,37 +4441,37 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">370
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">358
+          <t xml:space="preserve">558
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4401,36 +4483,36 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>63</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2329
+          <t xml:space="preserve">2323
 </t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
+          <t xml:space="preserve">512
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -4441,12 +4523,13 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t xml:space="preserve">90
+</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11941
+          <t xml:space="preserve">1941
 </t>
         </is>
       </c>
@@ -4458,17 +4541,22 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="2" t="n"/>
+          <t xml:space="preserve">429
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">283
+</t>
+        </is>
+      </c>
       <c r="Z30" s="2" t="n"/>
       <c r="AA30" t="inlineStr">
         <is>
@@ -4484,8 +4572,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2364
-</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4496,29 +4583,30 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t xml:space="preserve">50
+</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -4530,7 +4618,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
@@ -4559,34 +4647,28 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1551
-</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1424
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">826
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">6
+</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">388
@@ -4613,7 +4695,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4635,12 +4717,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
+      <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">338
@@ -4649,7 +4726,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -4661,31 +4738,31 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4720,36 +4797,37 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">285
+</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="X32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr"/>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Z32" s="2" t="n"/>
@@ -4768,13 +4846,12 @@
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>04444</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4792,7 +4869,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -4803,13 +4880,13 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">358
 </t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4821,24 +4898,25 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">57
+</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -4850,25 +4928,25 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1847
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1062
 </t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
+          <t xml:space="preserve">834
 </t>
         </is>
       </c>
@@ -4880,19 +4958,18 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Z33" s="2" t="n"/>
@@ -4916,7 +4993,8 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>321</t>
+          <t xml:space="preserve">312
+</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4945,7 +5023,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4963,12 +5041,13 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -4992,18 +5071,19 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">134
+</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5033,19 +5113,20 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">116
+178
 </t>
         </is>
       </c>
@@ -5063,19 +5144,18 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4379
+          <t xml:space="preserve">4339
 </t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>501</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0856
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -5093,7 +5173,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -5105,7 +5185,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -5123,20 +5203,25 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5160,38 +5245,37 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">550
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>431</t>
         </is>
       </c>
       <c r="Z35" s="2" t="n"/>
@@ -5209,13 +5293,13 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
@@ -5233,7 +5317,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -5246,13 +5330,12 @@
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>442</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -5267,21 +5350,16 @@
 </t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -5299,7 +5377,7 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5311,13 +5389,13 @@
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -5329,13 +5407,13 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Z36" s="2" t="n"/>
@@ -5354,45 +5432,43 @@
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1516
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">424
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>416</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">8219
 </t>
         </is>
       </c>
@@ -5402,21 +5478,16 @@
 </t>
         </is>
       </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3898
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
@@ -5428,18 +5499,18 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">478
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">341
 </t>
         </is>
       </c>
@@ -5456,22 +5527,26 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
+          <t xml:space="preserve">790
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>492</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
-</t>
-        </is>
-      </c>
-      <c r="Z37" s="2" t="n"/>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">962
+</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -5491,7 +5566,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">1856
 </t>
         </is>
       </c>
@@ -5503,7 +5578,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
@@ -5515,7 +5590,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -5527,7 +5602,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13010
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -5545,12 +5620,13 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t xml:space="preserve">532
+</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">478
 </t>
         </is>
       </c>
@@ -5560,21 +5636,16 @@
 </t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">879
-</t>
-        </is>
-      </c>
+      <c r="P38" s="2" t="inlineStr"/>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">1335
 </t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1485
 </t>
         </is>
       </c>
@@ -5586,37 +5657,38 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -5639,60 +5711,65 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>54441</t>
+          <t>54444</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2821
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>512</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr"/>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1060004</t>
+          <t>406</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
@@ -5722,13 +5799,13 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -5740,8 +5817,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
@@ -5752,14 +5828,13 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3964
+          <t xml:space="preserve">364
 </t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5774,15 +5849,11 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6171
-</t>
-        </is>
-      </c>
+      <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>303</t>
+          <t xml:space="preserve">292
+</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -5805,16 +5876,11 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
           <t>22</t>
@@ -5822,16 +5888,11 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1162
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">102
@@ -5840,41 +5901,22 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">610
-</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
+          <t>948</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="n"/>
+      <c r="P40" s="2" t="n"/>
       <c r="Q40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">287
 </t>
         </is>
       </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1150
-</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
+      <c r="R40" s="2" t="n"/>
+      <c r="S40" s="2" t="n"/>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8224
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -5898,19 +5940,19 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -5928,13 +5970,13 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -5945,31 +5987,31 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -5981,93 +6023,68 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">520
 </t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">360
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">150
+</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">326
-</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">275
-</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="X41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1975
+</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="n"/>
+      <c r="V41" s="2" t="n"/>
+      <c r="W41" s="2" t="n"/>
+      <c r="X41" s="2" t="n"/>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8289
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2236
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">289
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="n"/>
       <c r="AA41" t="inlineStr">
         <is>
           <t>28</t>
@@ -6080,15 +6097,23 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+4811
+</t>
+        </is>
+      </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t xml:space="preserve">314
+</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -6105,13 +6130,13 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1530
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -6123,37 +6148,37 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">2020
 </t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6165,54 +6190,54 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>455</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1655
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -6228,22 +6253,16 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3240
-</t>
-        </is>
-      </c>
+      <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -6254,37 +6273,36 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -6296,35 +6314,32 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
-      </c>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -6336,36 +6351,37 @@
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">1418
 </t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">2853
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -6383,19 +6399,19 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">3605
 </t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -6407,7 +6423,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -6419,48 +6435,49 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">5815
+</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -6472,13 +6489,13 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1844
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">8898
 </t>
         </is>
       </c>
@@ -6490,25 +6507,25 @@
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -6518,7 +6535,12 @@
 </t>
         </is>
       </c>
-      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>31</t>
@@ -6533,19 +6555,19 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1857
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1501
 </t>
         </is>
       </c>
@@ -6563,19 +6585,19 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3560
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
@@ -6587,86 +6609,87 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2265
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8818
-</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr"/>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t xml:space="preserve">528
+</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t xml:space="preserve">212
+</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1865
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1841
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">22
+11
 </t>
         </is>
       </c>
@@ -6684,25 +6707,25 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518
+          <t xml:space="preserve">2322
 </t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">1877
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11399
+          <t xml:space="preserve">12321
 </t>
         </is>
       </c>
@@ -6710,88 +6733,84 @@
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">350
 </t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">523
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
+          <t>5242</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0609
-</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t xml:space="preserve">622
+</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">494
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t xml:space="preserve">784
+</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1790
-</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t xml:space="preserve">5128
+</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr"/>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t xml:space="preserve">27
+</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">648
 </t>
         </is>
       </c>
@@ -6801,7 +6820,12 @@
 </t>
         </is>
       </c>
-      <c r="Z46" s="2" t="n"/>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">826
+</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -6814,28 +6838,44 @@
           <t>Tot.</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">588
+</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>916</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1053
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1211
-</t>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>68</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6844,15 +6884,33 @@
 </t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">391
+</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3292
 </t>
         </is>
       </c>
@@ -6862,7 +6920,49 @@
 </t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">308
+</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+2
+</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>Tot.</t>

--- a/results/05_transient_transcription_output/501/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/501/Top_Excel_with_OCR_Results.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">15698
 </t>
         </is>
       </c>
@@ -635,15 +635,10 @@
           <t>335</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
+      <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -656,7 +651,7 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
@@ -668,13 +663,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">355
@@ -689,18 +688,19 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>323</t>
+          <t xml:space="preserve">2383
+</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -710,42 +710,12 @@
 </t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">468
-</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">322
-</t>
-        </is>
-      </c>
+      <c r="U4" s="2" t="n"/>
+      <c r="V4" s="2" t="n"/>
+      <c r="W4" s="2" t="n"/>
+      <c r="X4" s="2" t="n"/>
+      <c r="Y4" s="2" t="n"/>
+      <c r="Z4" s="2" t="n"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1</t>
@@ -760,8 +730,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-2
+          <t xml:space="preserve">5127
 </t>
         </is>
       </c>
@@ -773,37 +742,36 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">2218
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>442</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -820,13 +788,13 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">355
+          <t xml:space="preserve">1655
 </t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -838,67 +806,63 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="n"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
+          <t xml:space="preserve">1468
 </t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1284
 </t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t xml:space="preserve">322
+</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -913,10 +877,15 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15048
+</t>
+        </is>
+      </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3321
+          <t xml:space="preserve">3348
 </t>
         </is>
       </c>
@@ -928,20 +897,19 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1206231
 </t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -952,99 +920,101 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">122
 </t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>94887</t>
-        </is>
-      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">1898
 </t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">408
-</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11400
+</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="n"/>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">1327
 </t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">424
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="n"/>
+          <t xml:space="preserve">2012
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2302
+</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>3</t>
@@ -1059,54 +1029,53 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536
+          <t xml:space="preserve">5836
 </t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>353</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>461</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">0080
 </t>
         </is>
       </c>
@@ -1118,20 +1087,13 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1142,61 +1104,60 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
+          <t xml:space="preserve">347
 </t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
+          <t xml:space="preserve">1424
 </t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
@@ -1214,64 +1175,63 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n"/>
+          <t xml:space="preserve">4851
+</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">344
+</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">11510
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1272
-</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1227
+</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1910
+</t>
+        </is>
+      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">71108
+</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">2365
 </t>
         </is>
       </c>
@@ -1289,52 +1249,54 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">1710
 </t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">422
+          <t xml:space="preserve">9422
 </t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>451</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">1153
+</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">1117
 </t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t xml:space="preserve">867
+</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>342</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1351,133 +1313,134 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26562</t>
+          <t xml:space="preserve">26360
+</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t xml:space="preserve">11697
+</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">533
-</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t xml:space="preserve">1164
+</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2262
-411464141
+          <t xml:space="preserve">391
 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">16442
 </t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">1684
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">2587
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1830
+          <t xml:space="preserve">11830
 </t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">497
+          <t xml:space="preserve">9497
 </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16850
+          <t xml:space="preserve">11690
 </t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr"/>
+          <t xml:space="preserve">718
+</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1277
+</t>
+        </is>
+      </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">12241
 </t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
+          <t xml:space="preserve">11397
 </t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">1696
 </t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">389
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">11862
 </t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">11202
 </t>
         </is>
       </c>
@@ -1495,19 +1458,18 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">2312
 </t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
@@ -1519,108 +1481,115 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">78
+</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1134
+</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2366
+</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">330
+</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">88
 </t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">366
-</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">330
-</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
+          <t xml:space="preserve">1448
 </t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1382
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1841
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -1638,36 +1607,31 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4229
+          <t xml:space="preserve">14278
 </t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">300
+</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>421</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1677,7 +1641,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
@@ -1689,35 +1653,35 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t xml:space="preserve">1130
+</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">9289
+</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11489
+</t>
+        </is>
+      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">88
@@ -1726,40 +1690,25 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2290
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">1310
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4240
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1217
+</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="n"/>
+      <c r="X11" s="2" t="n"/>
+      <c r="Y11" s="2" t="n"/>
       <c r="Z11" s="2" t="n"/>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1775,55 +1724,49 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
+          <t xml:space="preserve">20 6 1
 </t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7119
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>448</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1287
 </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -1835,42 +1778,42 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
+          <t xml:space="preserve">1530
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">3118
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">144
+</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -1882,33 +1825,37 @@
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1840
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="n"/>
+          <t xml:space="preserve">1023
+</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">470
+</t>
+        </is>
+      </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-76
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,25 +1872,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">613
+          <t xml:space="preserve">16013
 </t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">343
-</t>
+          <t>343</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
@@ -1955,7 +1901,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
@@ -1967,13 +1913,13 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">1157
 </t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1985,82 +1931,81 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">12490
 </t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">396
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">8332
 </t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">496
+          <t xml:space="preserve">1440
 </t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2872
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t xml:space="preserve">151
+</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">408
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="2" t="n"/>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12654
+</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>8</t>
@@ -2075,7 +2020,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
+          <t xml:space="preserve">14880
 </t>
         </is>
       </c>
@@ -2087,13 +2032,13 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
@@ -2105,7 +2050,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
@@ -2123,7 +2068,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">020
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -2135,79 +2080,67 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">1490
 </t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2303
+</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="n"/>
+      <c r="S14" s="2" t="n"/>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2360
+</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="n"/>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">1144
+</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t xml:space="preserve">82
+</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="Z14" s="2" t="n"/>
+          <t xml:space="preserve">0208
+</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4312
+</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>9</t>
@@ -2222,7 +2155,8 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5524</t>
+          <t xml:space="preserve">18329
+</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2232,29 +2166,31 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1795
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">1231
+</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t xml:space="preserve">102
+</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -2266,37 +2202,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
@@ -2306,36 +2237,21 @@
 </t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
+      <c r="R15" s="2" t="n"/>
+      <c r="S15" s="2" t="n"/>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
-</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">3820
+</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="n"/>
       <c r="W15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">140
@@ -2344,20 +2260,19 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2374,78 +2289,73 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25777
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">526
+          <t xml:space="preserve">12916
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>151</t>
+          <t xml:space="preserve">27268
+</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>821</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">353
+          <t xml:space="preserve">973
 </t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">562
+</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
-14
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8223
+          <t xml:space="preserve">1899
 </t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">443222
-181909191
-</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">29529
+</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21215
+          <t xml:space="preserve">22120
 </t>
         </is>
       </c>
@@ -2457,13 +2367,14 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">547
+          <t xml:space="preserve">11547
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>236</t>
+          <t xml:space="preserve">10836
+</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2474,44 +2385,43 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8206
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-7918949
+          <t xml:space="preserve">11882
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1315
+          <t xml:space="preserve">11310
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">483
+          <t xml:space="preserve">1483
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1488
+          <t xml:space="preserve">112458
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">11244
 </t>
         </is>
       </c>
@@ -2529,109 +2439,102 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">3154
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1236
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
+          <t xml:space="preserve">9425
 </t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0624
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3609
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>47</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
+          <t xml:space="preserve">1873
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">376
 </t>
         </is>
       </c>
@@ -2643,27 +2546,23 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
-        </is>
-      </c>
-      <c r="Z17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">449
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2292
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="n"/>
       <c r="AA17" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2678,134 +2577,125 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-2
+          <t xml:space="preserve">5321
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>349</t>
+          <t xml:space="preserve">029
+</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1124
+</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">166
+</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>29111</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t xml:space="preserve">1152
+</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t xml:space="preserve">1155
+</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3726
-</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1404
+</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="n"/>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">11844
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="Y18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="Z18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="n"/>
+      <c r="Z18" s="2" t="n"/>
       <c r="AA18" t="inlineStr">
         <is>
           <t>11</t>
@@ -2820,135 +2710,128 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-2975
+          <t xml:space="preserve">3264
 </t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1123
+</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1926
+</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1135
+</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1605
+</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">320
+</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1414
+</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="n"/>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">129
 </t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">608
-</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">320
-</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>962</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="X19" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
+      <c r="X19" s="2" t="n"/>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="Z19" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1220
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">297
+</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>12</t>
@@ -2961,18 +2844,16 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">446466240
-212
-79719019
-</t>
-        </is>
-      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
@@ -2983,19 +2864,19 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -3007,37 +2888,35 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">5220
 </t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -3049,7 +2928,8 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t xml:space="preserve">1146
+</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -3066,34 +2946,40 @@
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t xml:space="preserve">1222
+</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">11824
 </t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
-        </is>
-      </c>
-      <c r="Z20" s="2" t="n"/>
+          <t xml:space="preserve">520
+</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>13</t>
@@ -3114,66 +3000,61 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">1364
+</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1132
+</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">1775
 </t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
@@ -3184,7 +3065,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
@@ -3202,48 +3083,50 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">366
 </t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3260,39 +3143,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t xml:space="preserve">15363
+</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>348</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>435</t>
+          <t xml:space="preserve">12225
+</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t xml:space="preserve">1166
+</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
@@ -3304,31 +3190,27 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">1010
 </t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1107
+</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">510
+</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3339,36 +3221,36 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">145
+</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1849
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
+          <t xml:space="preserve">2390
 </t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -3380,17 +3262,22 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="2" t="n"/>
+          <t xml:space="preserve">2163
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1262
+</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>15</t>
@@ -3403,22 +3290,27 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2315
+</t>
+        </is>
+      </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">603
+          <t xml:space="preserve">1603
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">725
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">11171
 </t>
         </is>
       </c>
@@ -3430,8 +3322,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44255
-82947
+          <t xml:space="preserve">1600
 </t>
         </is>
       </c>
@@ -3443,51 +3334,56 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">7191
+</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">12120
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">1412
+</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">1544
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -3498,42 +3394,43 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t xml:space="preserve">1829
+</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920
+          <t xml:space="preserve">1872
 </t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">13026
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
+          <t xml:space="preserve">1688
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">1428
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">11224
 </t>
         </is>
       </c>
@@ -3551,7 +3448,8 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>50261</t>
+          <t xml:space="preserve">3095
+</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3562,45 +3460,41 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1784
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1114
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -3609,25 +3503,20 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">546
+          <t xml:space="preserve">046
 </t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3637,7 +3526,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
@@ -3648,19 +3537,19 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1872
+          <t xml:space="preserve">374
 </t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
@@ -3672,19 +3561,19 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3702,117 +3591,114 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4555
+          <t xml:space="preserve">4255
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2119
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>432</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1842
 </t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4008
+          <t xml:space="preserve">1400
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">11140
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">83
-</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="n"/>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1202
+</t>
+        </is>
+      </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-2
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-171111
+          <t xml:space="preserve">1177
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
@@ -3824,10 +3710,16 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z25" s="2" t="n"/>
+          <t xml:space="preserve">14575
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11121
+</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>16</t>
@@ -3854,12 +3746,13 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">1148
+</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">2225
 </t>
         </is>
       </c>
@@ -3871,44 +3764,43 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="n"/>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1089
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
@@ -3920,7 +3812,7 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
@@ -3932,46 +3824,46 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2664
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
-</t>
-        </is>
-      </c>
-      <c r="X26" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="n"/>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="2" t="n"/>
+          <t xml:space="preserve">2270
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1250
+</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>17</t>
@@ -3986,143 +3878,122 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">5501
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22858
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">106
+</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">985
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5280
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="n"/>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">1374
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="X27" s="2" t="inlineStr">
+          <t>48</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="n"/>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10266
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="Z27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-309
 </t>
         </is>
       </c>
@@ -4140,24 +4011,25 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6210
+          <t xml:space="preserve">16210
 </t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t xml:space="preserve">332
+</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
@@ -4169,13 +4041,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -4187,7 +4058,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -4199,80 +4070,87 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4280
+          <t xml:space="preserve">14280
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">11208
 </t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">321
+</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">434
+</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1277
+</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1133
+</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">308
 </t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45
-</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1660
-</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133
-</t>
-        </is>
-      </c>
-      <c r="X28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="Y28" s="2" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="Z28" s="2" t="n"/>
       <c r="AA28" t="inlineStr">
         <is>
           <t>19</t>
@@ -4287,22 +4165,25 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">6249
+</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">344
+</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">1122
+</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
@@ -4314,24 +4195,25 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">1008
 </t>
         </is>
       </c>
@@ -4343,55 +4225,54 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">1413
 </t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">3835
 </t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>456</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="n"/>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">1277
 </t>
         </is>
       </c>
@@ -4403,7 +4284,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -4413,7 +4294,12 @@
 </t>
         </is>
       </c>
-      <c r="Z29" s="2" t="n"/>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30682
+</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>20</t>
@@ -4426,52 +4312,57 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27819
+</t>
+        </is>
+      </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">1616
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">7145
 </t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1570
 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
+          <t xml:space="preserve">3720
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
+          <t xml:space="preserve">1558
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
@@ -4483,53 +4374,50 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t xml:space="preserve">1306
+</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2323
+          <t xml:space="preserve">2223
 </t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">512
+          <t xml:space="preserve">017
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">1531
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+          <t xml:space="preserve">709
+</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="n"/>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">726
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1941
+          <t xml:space="preserve">81941
 </t>
         </is>
       </c>
@@ -4541,22 +4429,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1668
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="n"/>
       <c r="Z30" s="2" t="n"/>
       <c r="AA30" t="inlineStr">
         <is>
@@ -4572,7 +4455,8 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t xml:space="preserve">2364
+</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4583,62 +4467,48 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>489</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1929
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1112
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">164
 </t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">506
-</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
-      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">465
@@ -4647,28 +4517,29 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t xml:space="preserve">310
+</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1424
-</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1142
+</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="n"/>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1145
+</t>
+        </is>
+      </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">388
@@ -4677,25 +4548,25 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">2293
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
@@ -4717,7 +4588,12 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0111
+</t>
+        </is>
+      </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">338
@@ -4726,52 +4602,56 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">112321
+</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">390
@@ -4784,53 +4664,46 @@
 </t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
+      <c r="Q32" s="2" t="n"/>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1141
+</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="n"/>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>4241</t>
-        </is>
-      </c>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="n"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">1283
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="X32" s="2" t="inlineStr"/>
-      <c r="Y32" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="Z32" s="2" t="n"/>
+          <t xml:space="preserve">1137
+</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">319
+</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>21</t>
@@ -4843,136 +4716,135 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4487
+</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>04444</t>
+          <t xml:space="preserve">308
+</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">2229
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1167
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t xml:space="preserve">111
+</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">358
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1410
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">336
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="n"/>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1062
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1147
+</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="n"/>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">834
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">303
+</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="n"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">12180
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>445</t>
+          <t xml:space="preserve">1135
+</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z33" s="2" t="n"/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>22</t>
@@ -4991,39 +4863,24 @@
 </t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">312
-</t>
-        </is>
-      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1232
+</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -5035,7 +4892,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -5047,86 +4904,85 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">11160
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">522
+          <t xml:space="preserve">129522
 </t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">0250
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">7190
 </t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">1127
 </t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">116
-178
 </t>
         </is>
       </c>
@@ -5150,48 +5006,44 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t xml:space="preserve">303
+</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1170
+</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1133
 </t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1285
 </t>
         </is>
       </c>
@@ -5203,37 +5055,32 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -5245,19 +5092,19 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
+          <t xml:space="preserve">2228
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
@@ -5275,10 +5122,15 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="Z35" s="2" t="n"/>
+          <t xml:space="preserve">18398
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>4221</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>24</t>
@@ -5293,130 +5145,132 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">3413
 </t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">211
+</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1123
 </t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1940
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z36" s="2" t="n"/>
+          <t xml:space="preserve">2188
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>25</t>
@@ -5429,94 +5283,114 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>9661</t>
+        </is>
+      </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">11816
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">1689
+</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">11102
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">827
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">424
+          <t xml:space="preserve">358
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1010
+</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8219
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1232
+</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">12402
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1335
 </t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">17826
+</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1478
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">341
+          <t xml:space="preserve">11410
 </t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">11342
+</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -5527,23 +5401,24 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">790
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t xml:space="preserve">9498
+</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t xml:space="preserve">1812
+</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
@@ -5561,133 +5436,125 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t xml:space="preserve">4433
+</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1856
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
-</t>
+          <t>428</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">21112
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">361
-</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
-</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">478
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
-</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr"/>
+          <t xml:space="preserve">14180
+</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1335
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1485
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">2269
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">374
 </t>
         </is>
       </c>
@@ -5711,35 +5578,37 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>54444</t>
+          <t xml:space="preserve">3146
+</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t xml:space="preserve">1292
+</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1142
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -5750,38 +5619,39 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr"/>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1132
+</t>
+        </is>
+      </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>406</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t xml:space="preserve">11102
+</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
-</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="n"/>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -5799,42 +5669,39 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1224
+</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="n"/>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">1150
+</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
+          <t xml:space="preserve">3964
 </t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t xml:space="preserve">2266
+</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5849,110 +5716,139 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6171
+</t>
+        </is>
+      </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1262217
 </t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="n"/>
+          <t xml:space="preserve">1112
+</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1086
+</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">183
+</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n"/>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1162
+</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>948</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="n"/>
-      <c r="P40" s="2" t="n"/>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">610
+</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="n"/>
-      <c r="S40" s="2" t="n"/>
+          <t xml:space="preserve">300
+</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1150
+</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
-</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">7942
+</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="n"/>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1847
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">81206
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">12216
 </t>
         </is>
       </c>
@@ -5970,121 +5866,141 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">5875
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">93
+</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1975
-</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="n"/>
-      <c r="V41" s="2" t="n"/>
-      <c r="W41" s="2" t="n"/>
-      <c r="X41" s="2" t="n"/>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2926
+</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1275
+</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="2" t="n"/>
+          <t xml:space="preserve">1288
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>28</t>
@@ -6099,145 +6015,137 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-4811
+          <t xml:space="preserve">4811
 </t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1233
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="n"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">9209
 </t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>464</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t xml:space="preserve">1147
+</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">1928
 </t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -6253,135 +6161,136 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3540
+</t>
+        </is>
+      </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t xml:space="preserve">164
+</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">2239
 </t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1041
 </t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t xml:space="preserve">197
+</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">915
+</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="n"/>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1289
+</t>
+        </is>
+      </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">2013
 </t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2853
+          <t xml:space="preserve">19253
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">2461
 </t>
         </is>
       </c>
@@ -6399,133 +6308,122 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2380
 </t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3605
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">6561
 </t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1909
+</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5815
+          <t xml:space="preserve">1440
 </t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1093
 </t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">1122
 </t>
         </is>
       </c>
@@ -6537,7 +6435,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1824
 </t>
         </is>
       </c>
@@ -6555,141 +6453,139 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">331029
 </t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">118715
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1501
+          <t xml:space="preserve">1919
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">11221
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">822246
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">15123
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">18222
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1110111
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">886
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18159
+</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">112265
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr"/>
+          <t xml:space="preserve">10218
+</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1838
+</t>
+        </is>
+      </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">18369
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">88886
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">214621
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1061
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">10987
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">12228
 </t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-11
+          <t xml:space="preserve">11172
 </t>
         </is>
       </c>
@@ -6707,122 +6603,123 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2322
+          <t xml:space="preserve">5518
 </t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1877
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12321
-</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1230
+</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">1494
 </t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>13321</t>
+          <t xml:space="preserve">1288
+</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5128
-</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr"/>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>7519</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
+          <t xml:space="preserve">3908
+</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="n"/>
+      <c r="W46" s="2" t="n"/>
+      <c r="X46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="X46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">648
-</t>
-        </is>
-      </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
@@ -6836,131 +6733,6 @@
       <c r="B47" t="inlineStr">
         <is>
           <t>Tot.</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">588
-</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>916</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">391
-</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">94
-</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3292
-</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">308
-</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-2
-</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">

--- a/results/05_transient_transcription_output/501/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/501/Top_Excel_with_OCR_Results.xlsx
@@ -626,19 +626,25 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15698
+          <t xml:space="preserve">5628
 </t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
+          <t xml:space="preserve">835
+</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">97
+</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -648,10 +654,15 @@
 </t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -663,20 +674,31 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">355
+          <t xml:space="preserve">345
 </t>
         </is>
       </c>
@@ -688,7 +710,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2383
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
@@ -700,7 +722,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
@@ -730,7 +752,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5127
+          <t xml:space="preserve">151 27 1
 </t>
         </is>
       </c>
@@ -742,59 +764,61 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2218
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">764
+</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t xml:space="preserve">1129
+</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1655
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -806,7 +830,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -818,7 +842,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">1840
 </t>
         </is>
       </c>
@@ -828,40 +852,44 @@
 </t>
         </is>
       </c>
-      <c r="T5" s="2" t="n"/>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>04449</t>
+        </is>
+      </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1468
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">968
 </t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">382
 </t>
         </is>
       </c>
@@ -879,13 +907,13 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15048
+          <t xml:space="preserve">23048
 </t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3348
+          <t xml:space="preserve">339
 </t>
         </is>
       </c>
@@ -903,13 +931,14 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206231
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t xml:space="preserve">75
+</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -926,7 +955,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -938,32 +967,37 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1898
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11400
-</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="n"/>
+          <t xml:space="preserve">21098
+</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1327
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -981,7 +1015,7 @@
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -993,7 +1027,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1642
 </t>
         </is>
       </c>
@@ -1005,13 +1039,13 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2302
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -1035,7 +1069,8 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t xml:space="preserve">353
+</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1046,13 +1081,13 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -1070,12 +1105,13 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t xml:space="preserve">169
+</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1087,13 +1123,15 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t xml:space="preserve">56
+</t>
         </is>
       </c>
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t xml:space="preserve">350
+</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1104,63 +1142,54 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">347
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">836
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">68
+</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1424
+          <t xml:space="preserve">017
 </t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1163
-</t>
-        </is>
-      </c>
-      <c r="Z7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">334
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="n"/>
+      <c r="Z7" s="2" t="n"/>
       <c r="AA7" t="inlineStr">
         <is>
           <t>4</t>
@@ -1175,63 +1204,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4851
+          <t xml:space="preserve">112851
 </t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11510
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
-</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
+          <t xml:space="preserve">2828
+</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">812
+</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
+          <t xml:space="preserve">0110
 </t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">1161
 </t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71108
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2365
+          <t xml:space="preserve">360
 </t>
         </is>
       </c>
@@ -1255,24 +1295,26 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1710
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">143
+</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422
+          <t xml:space="preserve">422
 </t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">2019
+</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1283,22 +1325,17 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">110982
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="n"/>
       <c r="AA8" t="inlineStr">
         <is>
           <t>5</t>
@@ -1313,13 +1350,13 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26360
+          <t xml:space="preserve">26660
 </t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11697
+          <t xml:space="preserve">1697
 </t>
         </is>
       </c>
@@ -1329,7 +1366,12 @@
 </t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14134
+</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1164
@@ -1338,55 +1380,61 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
+          <t xml:space="preserve">3291
 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16442
+          <t xml:space="preserve">6142
 </t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1684
+          <t xml:space="preserve">684
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">671
+</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">329
+</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2587
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11830
+          <t xml:space="preserve">1830
 </t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9497
+          <t xml:space="preserve">487
 </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11690
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
@@ -1398,7 +1446,7 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -1416,7 +1464,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11397
+          <t xml:space="preserve">1397
 </t>
         </is>
       </c>
@@ -1426,24 +1474,9 @@
 </t>
         </is>
       </c>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11862
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11202
-</t>
-        </is>
-      </c>
+      <c r="X9" s="2" t="n"/>
+      <c r="Y9" s="2" t="n"/>
+      <c r="Z9" s="2" t="n"/>
       <c r="AA9" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1464,12 +1497,13 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t xml:space="preserve">229
+</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">1872
 </t>
         </is>
       </c>
@@ -1481,19 +1515,19 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -1506,31 +1540,26 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366
+          <t xml:space="preserve">366
 </t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -1542,12 +1571,13 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">144
+</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -1559,40 +1589,35 @@
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1448
+          <t xml:space="preserve">1948
 </t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">992
+</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="n"/>
       <c r="AA10" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1607,44 +1632,58 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14278
+          <t xml:space="preserve">4279
 </t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">3080
+</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">139
+</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>06</t>
+          <t xml:space="preserve">1148
+</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">182
@@ -1653,11 +1692,11 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="n"/>
+          <t xml:space="preserve">614
+</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1130
@@ -1672,40 +1711,35 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9289
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11489
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">8220
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310
-</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1217
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">8210
+</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="n"/>
       <c r="W11" s="2" t="n"/>
       <c r="X11" s="2" t="n"/>
       <c r="Y11" s="2" t="n"/>
@@ -1724,24 +1758,24 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20 6 1
+          <t xml:space="preserve">2067
 </t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">517
 </t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1287
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
@@ -1753,20 +1787,25 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="n"/>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1784,36 +1823,37 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1530
+          <t xml:space="preserve">530
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">1100
+</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3118
+          <t xml:space="preserve">3108
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -1831,7 +1871,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -1843,19 +1883,20 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1023
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
+          <t xml:space="preserve">12170
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">18358
+</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,30 +1913,31 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16013
+          <t xml:space="preserve">6013
 </t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>343</t>
+          <t xml:space="preserve">343
+</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">1594
 </t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
@@ -1913,13 +1955,13 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1938,42 +1980,43 @@
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12490
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8332
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440
+          <t xml:space="preserve">440
 </t>
         </is>
       </c>
@@ -1985,25 +2028,25 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">1021
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t xml:space="preserve">088
+</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12654
-</t>
+          <t>865</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,7 +2063,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14880
+          <t xml:space="preserve">4890
 </t>
         </is>
       </c>
@@ -2032,112 +2075,133 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1244
+</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">490
+</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">144
 </t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1136
-</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1120
-</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1490
-</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1144
-</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2303
-</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="n"/>
-      <c r="S14" s="2" t="n"/>
+          <t xml:space="preserve">303
+</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t xml:space="preserve">169
+</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2360
-</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="n"/>
+          <t xml:space="preserve">360
+</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">270
+</t>
+        </is>
+      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0208
+          <t xml:space="preserve">0808
 </t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4312
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -2155,30 +2219,29 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18329
+          <t xml:space="preserve">2521
 </t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>343</t>
+          <t xml:space="preserve">315
+</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
+          <t>933</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -2190,7 +2253,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -2202,43 +2265,58 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="n"/>
+          <t xml:space="preserve">1104
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="n"/>
-      <c r="S15" s="2" t="n"/>
+          <t xml:space="preserve">3120
+</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1145
+</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1154
@@ -2247,14 +2325,18 @@
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3820
-</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="n"/>
+          <t xml:space="preserve">38208
+</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
@@ -2264,17 +2346,8 @@
 </t>
         </is>
       </c>
-      <c r="Y15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1234
-</t>
-        </is>
-      </c>
-      <c r="Z15" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
+      <c r="Y15" s="2" t="n"/>
+      <c r="Z15" s="2" t="n"/>
       <c r="AA15" t="inlineStr">
         <is>
           <t>10</t>
@@ -2289,36 +2362,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">2371
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12916
+          <t xml:space="preserve">1823916
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27268
+          <t xml:space="preserve">2168
 </t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t xml:space="preserve">1182
+</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
@@ -2336,23 +2410,28 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1899
+          <t xml:space="preserve">1898
 </t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29529
-</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2028
+</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">22120
@@ -2367,13 +2446,13 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11547
+          <t xml:space="preserve">1547
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10836
+          <t xml:space="preserve">836
 </t>
         </is>
       </c>
@@ -2391,37 +2470,37 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11882
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11310
+          <t xml:space="preserve">1315
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1483
+          <t xml:space="preserve">483
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112458
+          <t xml:space="preserve">11438
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11244
+          <t xml:space="preserve">10244
 </t>
         </is>
       </c>
@@ -2445,31 +2524,31 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">3819
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">22316
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -2485,22 +2564,28 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="2" t="n"/>
+      <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="n"/>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9425
+          <t xml:space="preserve">425
 </t>
         </is>
       </c>
@@ -2518,30 +2603,31 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1873
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t xml:space="preserve">1164
+</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">376
+          <t xml:space="preserve">9816
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2558,11 +2644,16 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2292
-</t>
-        </is>
-      </c>
-      <c r="Z17" s="2" t="n"/>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2577,25 +2668,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5321
+          <t xml:space="preserve">10321
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
+          <t xml:space="preserve">0229
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">827
 </t>
         </is>
       </c>
@@ -2607,18 +2697,18 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2629,7 +2719,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -2639,7 +2729,12 @@
 </t>
         </is>
       </c>
-      <c r="N18" s="2" t="n"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">175
@@ -2648,18 +2743,19 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>29111</t>
+          <t xml:space="preserve">2804
+</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -2671,26 +2767,31 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="n"/>
+          <t xml:space="preserve">404
+</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1081
+</t>
+        </is>
+      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11844
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -2710,20 +2811,18 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264
-</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
+          <t xml:space="preserve">354
 </t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2752,7 +2851,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1926
+          <t xml:space="preserve">11206
 </t>
         </is>
       </c>
@@ -2764,21 +2863,31 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
-</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2790,7 +2899,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -2802,24 +2911,34 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1414
-</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="n"/>
+          <t xml:space="preserve">1614
+</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">129
 </t>
         </is>
       </c>
-      <c r="X19" s="2" t="n"/>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67
+</t>
+        </is>
+      </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1220
@@ -2828,7 +2947,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -2846,31 +2965,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n"/>
+          <t xml:space="preserve">93905
+</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">9149
 </t>
         </is>
       </c>
@@ -2882,41 +3007,42 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t xml:space="preserve">07
+</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5220
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -2928,7 +3054,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -2952,34 +3078,29 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">16202
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11824
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
-        </is>
-      </c>
-      <c r="Z20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="n"/>
       <c r="AA20" t="inlineStr">
         <is>
           <t>13</t>
@@ -2994,55 +3115,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5422
+          <t xml:space="preserve">9422
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>302</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1364
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
-</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1775
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -3054,18 +3181,19 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t xml:space="preserve">490
+</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -3083,13 +3211,13 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -3101,19 +3229,19 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">2863
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -3125,7 +3253,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2176
 </t>
         </is>
       </c>
@@ -3143,13 +3271,14 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15363
+          <t xml:space="preserve">5363
 </t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t xml:space="preserve">318
+</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3160,19 +3289,19 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12225
+          <t xml:space="preserve">2125
 </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -3190,23 +3319,28 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
-</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="n"/>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">510
@@ -3221,7 +3355,8 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t xml:space="preserve">313
+</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
@@ -3232,19 +3367,19 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
@@ -3256,7 +3391,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
@@ -3268,13 +3403,13 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -3292,13 +3427,13 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2315
+          <t xml:space="preserve">25175
 </t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1603
+          <t xml:space="preserve">1605
 </t>
         </is>
       </c>
@@ -3310,19 +3445,18 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11171
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">1868
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600
+          <t xml:space="preserve">1610
 </t>
         </is>
       </c>
@@ -3346,55 +3480,55 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7191
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">503
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12120
+          <t xml:space="preserve">2720
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
+          <t xml:space="preserve">412
 </t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1544
+          <t xml:space="preserve">1344
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">735
 </t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
+          <t xml:space="preserve">566
 </t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1829
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
@@ -3406,7 +3540,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13026
+          <t xml:space="preserve">1388
 </t>
         </is>
       </c>
@@ -3418,7 +3552,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
@@ -3430,7 +3564,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11224
+          <t xml:space="preserve">11274
 </t>
         </is>
       </c>
@@ -3448,91 +3582,103 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3095
-</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">046
+</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">346
+</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">309
+</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">147
 </t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">046
-</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1147
-</t>
-        </is>
-      </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
@@ -3553,27 +3699,22 @@
 </t>
         </is>
       </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
+      <c r="W24" s="2" t="inlineStr"/>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="Z24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3591,42 +3732,44 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4255
+          <t xml:space="preserve">4555
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">177
+</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">5248
 </t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1842
+          <t xml:space="preserve">1142
 </t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">61
+</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3643,57 +3786,66 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="n"/>
+          <t xml:space="preserve">1218
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1400
+          <t xml:space="preserve">400
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11140
+          <t xml:space="preserve">1040
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="n"/>
+          <t xml:space="preserve">11480
+</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">873
+</t>
+        </is>
+      </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1177
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3710,13 +3862,13 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14575
+          <t xml:space="preserve">14114
 </t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11121
+          <t xml:space="preserve">218218280
 </t>
         </is>
       </c>
@@ -3734,7 +3886,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304
+          <t xml:space="preserve">2304
 </t>
         </is>
       </c>
@@ -3746,31 +3898,32 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2225
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">8055
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3781,26 +3934,31 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="n"/>
+          <t xml:space="preserve">1105
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">8120
 </t>
         </is>
       </c>
@@ -3812,19 +3970,20 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1142
 </t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3841,27 +4000,31 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X26" s="2" t="n"/>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2270
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3884,24 +4047,25 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">31 18
+</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">12356
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
@@ -3911,22 +4075,27 @@
 </t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1014
 </t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">1679
 </t>
         </is>
       </c>
@@ -3936,7 +4105,12 @@
 </t>
         </is>
       </c>
-      <c r="N27" s="2" t="n"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">220
@@ -3957,10 +4131,16 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="n"/>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1160
@@ -3969,31 +4149,32 @@
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1374
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="X27" s="2" t="n"/>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10266
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">18659
 </t>
         </is>
       </c>
@@ -4011,143 +4192,144 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16210
-</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">352
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">104646
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1816
+</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1004
+</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1420
+</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11010
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321
+</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2681
+</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1277
+</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1133
+</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">186
 </t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1102
-</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14280
-</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11208
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321
-</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">434
-</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1277
-</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1133
-</t>
-        </is>
-      </c>
-      <c r="X28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="Y28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
@@ -4165,7 +4347,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6249
+          <t xml:space="preserve">6248
 </t>
         </is>
       </c>
@@ -4177,13 +4359,13 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">1221
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -4195,25 +4377,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>497</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1008
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -4225,18 +4406,19 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1413
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -4248,7 +4430,7 @@
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3835
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
@@ -4260,7 +4442,8 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t xml:space="preserve">46
+</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -4269,10 +4452,15 @@
 </t>
         </is>
       </c>
-      <c r="U29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">421
+</t>
+        </is>
+      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
+          <t xml:space="preserve">2757
 </t>
         </is>
       </c>
@@ -4290,13 +4478,13 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30682
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -4314,7 +4502,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27819
+          <t xml:space="preserve">21819
 </t>
         </is>
       </c>
@@ -4326,7 +4514,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7145
+          <t xml:space="preserve">7265
 </t>
         </is>
       </c>
@@ -4338,7 +4526,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
@@ -4350,19 +4538,19 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1558
+          <t xml:space="preserve">1398
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
@@ -4374,13 +4562,13 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1306
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
@@ -4398,7 +4586,7 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">1591
 </t>
         </is>
       </c>
@@ -4408,16 +4596,21 @@
 </t>
         </is>
       </c>
-      <c r="S30" s="2" t="n"/>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">318
+</t>
+        </is>
+      </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81941
+          <t xml:space="preserve">11941
 </t>
         </is>
       </c>
@@ -4435,12 +4628,21 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="2" t="n"/>
-      <c r="Z30" s="2" t="n"/>
+          <t xml:space="preserve">11900
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4455,7 +4657,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2364
+          <t xml:space="preserve">8564
 </t>
         </is>
       </c>
@@ -4467,7 +4669,8 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t xml:space="preserve">149
+</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4478,8 +4681,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -4500,15 +4702,30 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="2" t="n"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">015
+</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">164
 </t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="n"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110 1
+</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">465
@@ -4529,14 +4746,18 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="n"/>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -4548,25 +4769,25 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2293
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -4590,13 +4811,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0111
-</t>
+          <t>61444</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">338
+          <t xml:space="preserve">3008
 </t>
         </is>
       </c>
@@ -4608,24 +4828,26 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112321
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">621
+</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">942
+</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -4636,22 +4858,28 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">11260
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="n"/>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">390
@@ -4660,34 +4888,49 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="n"/>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">336
+</t>
+        </is>
+      </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1141
 </t>
         </is>
       </c>
-      <c r="S32" s="2" t="n"/>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="U32" s="2" t="n"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">474
+</t>
+        </is>
+      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1283
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -4697,10 +4940,15 @@
 </t>
         </is>
       </c>
-      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">349
 </t>
         </is>
       </c>
@@ -4718,25 +4966,25 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4487
+          <t xml:space="preserve">6137
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
@@ -4766,13 +5014,13 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -4784,46 +5032,56 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1410
-</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1128
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="n"/>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1147
 </t>
         </is>
       </c>
-      <c r="S33" s="2" t="n"/>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="n"/>
+          <t xml:space="preserve">302
+</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1834
+</t>
+        </is>
+      </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12180
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">2617
 </t>
         </is>
       </c>
@@ -4835,13 +5093,13 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">14554
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">1039
 </t>
         </is>
       </c>
@@ -4859,28 +5117,42 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3866
-</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n"/>
+          <t>38463</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">308
+</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">1056
 </t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
-</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">018
+</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4898,31 +5170,31 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11160
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129522
+          <t xml:space="preserve">422
 </t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -4934,55 +5206,55 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">1324
 </t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7190
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1127
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">0118
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1010
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">18606
 </t>
         </is>
       </c>
@@ -5000,87 +5272,97 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339
+          <t xml:space="preserve">4399
 </t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">503
+</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1170
+</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1237
+</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1149
+</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1143
+</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">886
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">303
 </t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1170
-</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1133
-</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1285
-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1240
-</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
@@ -5092,19 +5374,19 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2111
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -5116,19 +5398,20 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18398
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5155,60 +5438,70 @@
 </t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">112
 </t>
         </is>
       </c>
-      <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
-</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1940
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5220,30 +5513,31 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">28221
 </t>
         </is>
       </c>
@@ -5255,19 +5549,19 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188
+          <t xml:space="preserve">14988
 </t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
@@ -5285,12 +5579,13 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>9661</t>
+          <t xml:space="preserve">22166
+</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11816
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -5302,7 +5597,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11102
+          <t xml:space="preserve">110253
 </t>
         </is>
       </c>
@@ -5314,7 +5609,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">358
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -5326,30 +5621,32 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">10180
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>364</t>
+          <t xml:space="preserve">86
+</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">017
+</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -5360,65 +5657,67 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t xml:space="preserve">5935
+</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1335
+          <t xml:space="preserve">1336
 </t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17826
+          <t xml:space="preserve">726
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1478
+          <t xml:space="preserve">478
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11410
+          <t xml:space="preserve">1516
 </t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11342
+          <t xml:space="preserve">1340
 </t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">870
+</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9498
+          <t xml:space="preserve">498
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">13150
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
@@ -5436,101 +5735,115 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433
+          <t xml:space="preserve">4733
 </t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>428</t>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1681
+</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1192
+</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1106
+</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">169
 </t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21112
-</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14180
-</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1267
-</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2269
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -5578,95 +5891,106 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3146
+          <t xml:space="preserve">9146
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">11921
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">114126
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">12119
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">102101
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15101
+</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1102
+</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2110
+</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8187
+</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1593
+</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">100
 </t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1132
-</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11102
-</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="n"/>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1224
@@ -5675,32 +5999,37 @@
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
-</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="n"/>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1248
+</t>
+        </is>
+      </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3964
+          <t xml:space="preserve">964
 </t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -5718,23 +6047,24 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6171
-</t>
+          <t>64716</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>303</t>
+          <t xml:space="preserve">917
+</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262217
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
@@ -5746,25 +6076,25 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1086
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
@@ -5782,7 +6112,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">801
 </t>
         </is>
       </c>
@@ -5806,28 +6136,34 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">87
+</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7942
-</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="n"/>
+          <t xml:space="preserve">3942
+</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1847
@@ -5836,19 +6172,19 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">2161
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81206
+          <t xml:space="preserve">380
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12216
+          <t xml:space="preserve">2216 3
 </t>
         </is>
       </c>
@@ -5872,12 +6208,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">1622
 </t>
         </is>
       </c>
@@ -5889,7 +6225,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">116621
 </t>
         </is>
       </c>
@@ -5913,7 +6249,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
@@ -5925,11 +6261,16 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="n"/>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">490
@@ -5938,7 +6279,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
@@ -5950,7 +6291,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -5962,19 +6303,19 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2926
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1275
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -5986,21 +6327,17 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1016
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18284
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
           <t>28</t>
@@ -6021,47 +6358,49 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t xml:space="preserve">3121
+</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -6077,10 +6416,15 @@
 </t>
         </is>
       </c>
-      <c r="N42" s="2" t="n"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95
+</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9209
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
@@ -6092,30 +6436,31 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t xml:space="preserve">204
+</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -6127,28 +6472,23 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="n"/>
       <c r="AA42" t="inlineStr">
         <is>
           <t>29</t>
@@ -6163,13 +6503,13 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3540
+          <t xml:space="preserve">2540
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">3056
 </t>
         </is>
       </c>
@@ -6181,7 +6521,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2239
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -6199,18 +6539,19 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t xml:space="preserve">59
+</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6220,23 +6561,33 @@
 </t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
-</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="n"/>
+          <t xml:space="preserve">9216
+</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -6248,31 +6599,31 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -6284,13 +6635,13 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19253
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2461
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -6308,7 +6659,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2380
+          <t xml:space="preserve">2280
 </t>
         </is>
       </c>
@@ -6326,7 +6677,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">12229
 </t>
         </is>
       </c>
@@ -6336,29 +6687,40 @@
 </t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6561
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
-</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="n"/>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -6375,13 +6737,13 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -6393,19 +6755,19 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1093
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -6423,7 +6785,7 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
@@ -6435,7 +6797,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1824
+          <t xml:space="preserve">11221
 </t>
         </is>
       </c>
@@ -6451,144 +6813,140 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">331029
-</t>
-        </is>
-      </c>
+      <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118715
+          <t xml:space="preserve">15551
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1919
+          <t xml:space="preserve">4119
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11221
+          <t xml:space="preserve">11021
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822246
+          <t xml:space="preserve">3450
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15123
+          <t xml:space="preserve">2263
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18222
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110111
+          <t xml:space="preserve">12919
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18159
-</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr"/>
+          <t xml:space="preserve">801
+</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112265
+          <t xml:space="preserve">1022615
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">9204
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t xml:space="preserve">1284
+</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10218
+          <t xml:space="preserve">0118
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1838
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18369
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88886
+          <t xml:space="preserve">1026
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214621
+          <t xml:space="preserve">1412
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1061
+          <t xml:space="preserve">01010
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10987
+          <t xml:space="preserve">18 8
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12228
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11172
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12224
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6603,13 +6961,13 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518
-</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t xml:space="preserve">706
+</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -6620,25 +6978,26 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">9010
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -6647,23 +7006,28 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="2" t="n"/>
+      <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1808
+</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
@@ -6675,13 +7039,13 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -6693,27 +7057,37 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3908
-</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="n"/>
-      <c r="W46" s="2" t="n"/>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">848
+</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1144
+</t>
+        </is>
+      </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/501/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/501/Top_Excel_with_OCR_Results.xlsx
@@ -626,19 +626,19 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5628
+          <t xml:space="preserve">5698
 </t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">937
 </t>
         </is>
       </c>
@@ -656,7 +656,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -686,13 +686,13 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -710,13 +710,13 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -752,8 +752,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151 27 1
-</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -764,7 +763,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
@@ -776,13 +775,13 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">764
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -794,19 +793,19 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -818,7 +817,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
@@ -854,12 +853,13 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>04449</t>
+          <t xml:space="preserve">122
+</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -883,13 +883,13 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
@@ -907,7 +907,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23048
+          <t xml:space="preserve">3068
 </t>
         </is>
       </c>
@@ -925,13 +925,13 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2231
 </t>
         </is>
       </c>
@@ -943,79 +943,79 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1008
+</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">85
 </t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">327
+</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">122
 </t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21098
-</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">327
-</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">0910
 </t>
         </is>
       </c>
@@ -1027,8 +1027,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
@@ -1039,13 +1038,13 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -1093,13 +1092,13 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -1111,7 +1110,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1123,7 +1122,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -1142,31 +1141,30 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">347
 </t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -1178,14 +1176,12 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>863</t>
         </is>
       </c>
       <c r="Y7" s="2" t="n"/>
@@ -1204,7 +1200,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112851
+          <t xml:space="preserve">2851
 </t>
         </is>
       </c>
@@ -1222,7 +1218,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2828
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -1240,25 +1236,25 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0110
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1161
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -1271,7 +1267,7 @@
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">32620
 </t>
         </is>
       </c>
@@ -1295,7 +1291,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
@@ -1313,25 +1309,25 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110982
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -1350,28 +1346,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26660
-</t>
+          <t>196565</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1697
+          <t xml:space="preserve">11697
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14134
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">383
+</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1164
@@ -1380,25 +1370,25 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3291
+          <t xml:space="preserve">391
 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6142
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">1684
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -1410,7 +1400,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
@@ -1428,7 +1418,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">487
+          <t xml:space="preserve">497
 </t>
         </is>
       </c>
@@ -1491,25 +1481,25 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">5312
 </t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1872
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -1521,8 +1511,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1559,7 +1548,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -1577,7 +1566,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -1589,7 +1578,7 @@
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">448
 </t>
         </is>
       </c>
@@ -1607,13 +1596,13 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -1638,8 +1627,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3080
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1650,25 +1638,25 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -1680,7 +1668,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -1692,11 +1680,16 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
-</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1130
@@ -1717,25 +1710,25 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8210
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -1764,24 +1757,19 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
-</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">10217
 </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -1805,7 +1793,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
@@ -1841,19 +1829,19 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3108
+          <t xml:space="preserve">3118
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -1865,7 +1853,7 @@
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -1883,19 +1871,19 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">1623
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12170
+          <t xml:space="preserve">14170
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18358
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -1925,7 +1913,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1594
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -1937,20 +1925,14 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1980,7 +1962,7 @@
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">8490
 </t>
         </is>
       </c>
@@ -1998,7 +1980,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
@@ -2028,25 +2010,24 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1021
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">088
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2075,7 +2056,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -2087,7 +2068,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -2111,7 +2092,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -2123,13 +2104,13 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -2153,55 +2134,55 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">045
+</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">738
+</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">360
+</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">270
+</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">145
 </t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">360
-</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">270
-</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0808
+          <t xml:space="preserve">10208
 </t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">2312
 </t>
         </is>
       </c>
@@ -2219,29 +2200,28 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2521
+          <t xml:space="preserve">26521
 </t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>731</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
@@ -2277,7 +2257,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -2289,7 +2269,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1488
 </t>
         </is>
       </c>
@@ -2301,48 +2281,42 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3120
-</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1145
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">310
+</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr"/>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">2008
 </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38208
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>981</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -2362,25 +2336,25 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2371
+          <t xml:space="preserve">2572
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1823916
+          <t xml:space="preserve">82916
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2168
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">11182
 </t>
         </is>
       </c>
@@ -2410,31 +2384,26 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1898
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22120
+          <t xml:space="preserve">22125
 </t>
         </is>
       </c>
@@ -2446,7 +2415,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1547
+          <t xml:space="preserve">1847
 </t>
         </is>
       </c>
@@ -2464,25 +2433,25 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1315
+          <t xml:space="preserve">1313
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -2494,7 +2463,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11438
+          <t xml:space="preserve">1458
 </t>
         </is>
       </c>
@@ -2518,31 +2487,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3154
+          <t xml:space="preserve">23134
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3819
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22316
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -2564,16 +2532,21 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">2104
 </t>
         </is>
       </c>
@@ -2585,7 +2558,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
+          <t xml:space="preserve">428
 </t>
         </is>
       </c>
@@ -2609,7 +2582,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
@@ -2621,7 +2594,7 @@
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9816
+          <t xml:space="preserve">9274
 </t>
         </is>
       </c>
@@ -2650,7 +2623,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -2668,7 +2641,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10321
+          <t xml:space="preserve">2321
 </t>
         </is>
       </c>
@@ -2680,7 +2653,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2689,26 +2662,21 @@
 </t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2731,7 +2699,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -2749,13 +2717,13 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2804
+          <t xml:space="preserve">2806
 </t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -2767,7 +2735,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
@@ -2779,7 +2747,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1081
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
@@ -2791,7 +2759,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -2811,18 +2779,19 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">354
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2843,15 +2812,10 @@
 </t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11206
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -2863,8 +2827,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2875,7 +2838,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
@@ -2905,7 +2868,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
@@ -2917,14 +2880,13 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1614
+          <t xml:space="preserve">414
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>969</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2941,13 +2903,13 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">2928
 </t>
         </is>
       </c>
@@ -2965,26 +2927,23 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93905
-</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2995,7 +2954,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9149
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -3007,7 +2966,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3018,7 +2977,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -3030,13 +2989,13 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">550
 </t>
         </is>
       </c>
@@ -3066,8 +3025,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>448</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -3078,25 +3036,25 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16202
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -3115,25 +3073,25 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9422
+          <t xml:space="preserve">0422
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1864
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -3151,7 +3109,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
@@ -3163,13 +3121,13 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">1757
 </t>
         </is>
       </c>
@@ -3235,7 +3193,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -3247,13 +3205,13 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2176
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -3271,7 +3229,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363
+          <t xml:space="preserve">9363
 </t>
         </is>
       </c>
@@ -3289,7 +3247,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -3337,7 +3295,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -3373,13 +3331,13 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">1849
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">2390
 </t>
         </is>
       </c>
@@ -3391,13 +3349,13 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
@@ -3433,30 +3391,31 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
+          <t xml:space="preserve">1603
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">735
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t xml:space="preserve">11171
+</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1868
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1610
+          <t xml:space="preserve">1600
 </t>
         </is>
       </c>
@@ -3480,7 +3439,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -3492,37 +3451,37 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2720
+          <t xml:space="preserve">12720
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
+          <t xml:space="preserve">413
 </t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1344
+          <t xml:space="preserve">2544
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">735
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
+          <t xml:space="preserve">3686
 </t>
         </is>
       </c>
@@ -3540,13 +3499,13 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388
+          <t xml:space="preserve">1386
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1688
+          <t xml:space="preserve">688
 </t>
         </is>
       </c>
@@ -3564,7 +3523,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11274
+          <t xml:space="preserve">11224
 </t>
         </is>
       </c>
@@ -3582,12 +3541,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
@@ -3599,7 +3558,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">2234
 </t>
         </is>
       </c>
@@ -3611,7 +3570,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">1022
 </t>
         </is>
       </c>
@@ -3623,16 +3582,11 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1174
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -3641,19 +3595,19 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">046
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">346
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -3665,7 +3619,7 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -3683,7 +3637,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -3699,7 +3653,11 @@
 </t>
         </is>
       </c>
-      <c r="W24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">86
@@ -3708,13 +3666,13 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3750,7 +3708,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5248
+          <t xml:space="preserve">10248
 </t>
         </is>
       </c>
@@ -3792,42 +3750,43 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
+          <t xml:space="preserve">4010
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1040
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11480
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">873
+          <t xml:space="preserve">8373
 </t>
         </is>
       </c>
@@ -3839,18 +3798,18 @@
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>37</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -3862,13 +3821,12 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14114
-</t>
+          <t>416</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218218280
+          <t xml:space="preserve">11121
 </t>
         </is>
       </c>
@@ -3886,7 +3844,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2304
+          <t xml:space="preserve">5304
 </t>
         </is>
       </c>
@@ -3910,7 +3868,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8055
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
@@ -3958,7 +3916,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8120
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -3970,13 +3928,12 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
-</t>
+          <t>993</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -3988,7 +3945,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -4000,13 +3957,13 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -4018,13 +3975,13 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">0220
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4041,13 +3998,13 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5501
+          <t xml:space="preserve">501
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31 18
+          <t xml:space="preserve">318 4
 </t>
         </is>
       </c>
@@ -4059,13 +4016,13 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12356
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -4083,7 +4040,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1014
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
@@ -4095,7 +4052,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1679
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -4107,19 +4064,19 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
@@ -4143,23 +4100,27 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">3174
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr"/>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
@@ -4168,13 +4129,12 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18659
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
@@ -4192,36 +4152,37 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t xml:space="preserve">16210
+</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">352
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104646
+          <t xml:space="preserve">1376
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1816
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
@@ -4263,20 +4224,19 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1420
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11010
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -4287,19 +4247,19 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2681
+          <t xml:space="preserve">434
 </t>
         </is>
       </c>
@@ -4311,7 +4271,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -4327,12 +4287,7 @@
 </t>
         </is>
       </c>
-      <c r="Z28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">908
-</t>
-        </is>
-      </c>
+      <c r="Z28" s="2" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
           <t>19</t>
@@ -4359,13 +4314,13 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -4383,18 +4338,18 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>493</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">81811
 </t>
         </is>
       </c>
@@ -4418,19 +4373,19 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">413
 </t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
@@ -4454,13 +4409,13 @@
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">421
+          <t xml:space="preserve">471
 </t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2757
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -4472,19 +4427,19 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">230090
 </t>
         </is>
       </c>
@@ -4502,19 +4457,19 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21819
+          <t xml:space="preserve">22819
 </t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616
+          <t xml:space="preserve">15616
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7265
+          <t xml:space="preserve">7145
 </t>
         </is>
       </c>
@@ -4526,13 +4481,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1570
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -4544,7 +4499,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1398
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -4580,20 +4535,19 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
+          <t xml:space="preserve">917
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1591
+          <t xml:space="preserve">1551
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">709
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -4604,13 +4558,13 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11941
+          <t xml:space="preserve">1941
 </t>
         </is>
       </c>
@@ -4628,19 +4582,19 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11900
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">1069
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4657,7 +4611,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8564
+          <t xml:space="preserve">2364
 </t>
         </is>
       </c>
@@ -4681,7 +4635,8 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -4698,13 +4653,13 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">015
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -4752,7 +4707,8 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">69
+</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
@@ -4811,13 +4767,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>611</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3008
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4834,19 +4789,19 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">621
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -4858,19 +4813,19 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11260
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -4888,7 +4843,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -4900,7 +4855,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -4924,7 +4879,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">1283
 </t>
         </is>
       </c>
@@ -4936,7 +4891,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -4948,7 +4903,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">349
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -4966,7 +4921,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6137
+          <t xml:space="preserve">1225
 </t>
         </is>
       </c>
@@ -4978,7 +4933,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -4990,7 +4945,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -5002,7 +4957,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5014,7 +4969,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -5038,11 +4993,16 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr"/>
+          <t xml:space="preserve">410
+</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">260
@@ -5051,7 +5011,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -5063,25 +5023,25 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
+          <t xml:space="preserve">1934
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2617
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -5093,14 +5053,13 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14554
+          <t xml:space="preserve">1492
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1039
-</t>
+          <t>432</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5117,7 +5076,8 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>38463</t>
+          <t xml:space="preserve">3866
+</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -5140,121 +5100,121 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1814
+</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">018
 </t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1172
-</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422
-</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1324
-</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1890
-</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="X34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0118
-</t>
-        </is>
-      </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18606
+          <t xml:space="preserve">180 16
 </t>
         </is>
       </c>
@@ -5284,13 +5244,13 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -5302,7 +5262,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -5314,13 +5274,13 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -5338,7 +5298,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -5350,19 +5310,14 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">303
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">986
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -5380,7 +5335,7 @@
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2111
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
@@ -5404,16 +5359,11 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="Z35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">21215
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
           <t>24</t>
@@ -5447,34 +5397,23 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">178
@@ -5489,13 +5428,13 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -5525,7 +5464,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -5537,7 +5476,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28221
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -5555,13 +5494,13 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14988
+          <t xml:space="preserve">11860
 </t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -5585,7 +5524,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">118106
 </t>
         </is>
       </c>
@@ -5597,7 +5536,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110253
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
@@ -5609,7 +5548,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">338
 </t>
         </is>
       </c>
@@ -5621,31 +5560,31 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10180
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">032
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
@@ -5657,31 +5596,31 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5935
+          <t xml:space="preserve">893
 </t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1336
+          <t xml:space="preserve">133 5
 </t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">478
+          <t xml:space="preserve">1478
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1516
+          <t xml:space="preserve">11510
 </t>
         </is>
       </c>
@@ -5693,13 +5632,13 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">670
 </t>
         </is>
       </c>
@@ -5711,13 +5650,13 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13150
+          <t xml:space="preserve">11812
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
@@ -5735,13 +5674,13 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4733
+          <t xml:space="preserve">4422
 </t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">2303
 </t>
         </is>
       </c>
@@ -5759,13 +5698,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1681
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -5783,7 +5722,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
@@ -5795,31 +5734,31 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
@@ -5831,7 +5770,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -5843,7 +5782,7 @@
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -5897,25 +5836,24 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11921
-</t>
+          <t>794</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114126
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12119
+          <t xml:space="preserve">11866
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102101
+          <t xml:space="preserve">108110
 </t>
         </is>
       </c>
@@ -5927,13 +5865,13 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -5945,25 +5883,24 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15101
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2110
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -5975,13 +5912,13 @@
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8187
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1593
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -5993,19 +5930,19 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">0294
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -6017,13 +5954,13 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">964
+          <t xml:space="preserve">364
 </t>
         </is>
       </c>
@@ -6047,12 +5984,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>64716</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
+          <t xml:space="preserve">907
 </t>
         </is>
       </c>
@@ -6064,7 +6001,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -6076,13 +6013,13 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -6094,7 +6031,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -6112,7 +6049,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -6136,7 +6073,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
@@ -6154,7 +6091,7 @@
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3942
+          <t xml:space="preserve">842
 </t>
         </is>
       </c>
@@ -6166,26 +6103,25 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1847
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2161
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216 3
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6208,12 +6144,13 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t xml:space="preserve">314
+</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1622
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -6225,19 +6162,19 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116621
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -6249,7 +6186,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6273,13 +6210,13 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
@@ -6303,13 +6240,13 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
@@ -6321,7 +6258,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -6331,13 +6268,12 @@
 </t>
         </is>
       </c>
-      <c r="Y41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18284
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>28</t>
@@ -6358,37 +6294,37 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3121
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6406,7 +6342,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -6418,13 +6354,13 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -6436,7 +6372,7 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -6448,13 +6384,13 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -6472,19 +6408,19 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6503,13 +6439,13 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2540
+          <t xml:space="preserve">5340
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3056
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -6533,7 +6469,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">1834
 </t>
         </is>
       </c>
@@ -6563,19 +6499,19 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9216
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -6593,7 +6529,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -6611,7 +6547,7 @@
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -6623,7 +6559,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -6641,7 +6577,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
@@ -6671,13 +6607,13 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12229
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -6707,7 +6643,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -6719,19 +6655,18 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -6749,25 +6684,25 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">1123
 </t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">3228
 </t>
         </is>
       </c>
@@ -6779,28 +6714,22 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11221
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">508
+</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
           <t>31</t>
@@ -6813,58 +6742,63 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18011
+</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15551
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4119
+          <t xml:space="preserve">917
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11021
+          <t xml:space="preserve">11221
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450
+          <t xml:space="preserve">7211
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2263
+          <t xml:space="preserve">523
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12919
+          <t xml:space="preserve">12818
 </t>
         </is>
       </c>
@@ -6876,73 +6810,68 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022615
+          <t xml:space="preserve">12265
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9204
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
+          <t xml:space="preserve">1700
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0118
+          <t xml:space="preserve">0815
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
-</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1026
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1264
+</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
+          <t xml:space="preserve">1442
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01010
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 8
+          <t xml:space="preserve">1 1
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12224
+          <t xml:space="preserve">12229
 </t>
         </is>
       </c>
@@ -6961,30 +6890,30 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">706
+          <t xml:space="preserve">406
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9010
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -6996,7 +6925,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -7006,7 +6935,12 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">168
@@ -7027,7 +6961,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">494
 </t>
         </is>
       </c>
@@ -7045,7 +6979,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -7063,19 +6997,19 @@
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
@@ -7087,13 +7021,13 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">1126
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/501/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/501/Top_Excel_with_OCR_Results.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">937
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -656,7 +656,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -674,7 +674,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -692,13 +692,13 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">345
+          <t xml:space="preserve">355
 </t>
         </is>
       </c>
@@ -710,19 +710,19 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -752,7 +752,8 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t xml:space="preserve">5127
+</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -763,19 +764,19 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
@@ -799,7 +800,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
@@ -811,19 +812,14 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">1360
 </t>
         </is>
       </c>
@@ -841,7 +837,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1840
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -853,37 +849,37 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1468
+</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">968
 </t>
         </is>
       </c>
@@ -907,7 +903,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3068
+          <t xml:space="preserve">5048
 </t>
         </is>
       </c>
@@ -931,7 +927,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2231
+          <t xml:space="preserve">20239
 </t>
         </is>
       </c>
@@ -943,7 +939,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -955,13 +951,13 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -971,21 +967,16 @@
 </t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+      <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1008
+          <t xml:space="preserve">1400
 </t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -997,13 +988,13 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -1015,7 +1006,7 @@
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0910
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
@@ -1027,7 +1018,8 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">142
+</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
@@ -1044,7 +1036,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">2302
 </t>
         </is>
       </c>
@@ -1068,13 +1060,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">353
-</t>
+          <t>353</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -1086,13 +1077,13 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -1110,7 +1101,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1122,11 +1113,16 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="n"/>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">350
@@ -1147,45 +1143,58 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">1138
+</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">424
 </t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>863</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="n"/>
-      <c r="Z7" s="2" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1163
+</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">334
+</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>4</t>
@@ -1200,13 +1209,13 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2851
+          <t xml:space="preserve">4851
 </t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">344
 </t>
         </is>
       </c>
@@ -1230,44 +1239,44 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32620
+          <t xml:space="preserve">362
 </t>
         </is>
       </c>
@@ -1297,41 +1306,45 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1133
+</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">143
 </t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr">
+      <c r="Y8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">422
 </t>
         </is>
       </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="X8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="Y8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="2" t="n"/>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>5</t>
@@ -1346,22 +1359,28 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>196565</t>
+          <t xml:space="preserve">26361
+</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11697
+          <t xml:space="preserve">1697
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">383
-</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1233
+</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11134
+</t>
+        </is>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1164
@@ -1376,25 +1395,25 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">442
 </t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1684
+          <t xml:space="preserve">684
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">671
+          <t xml:space="preserve">1671
 </t>
         </is>
       </c>
@@ -1406,37 +1425,37 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1830
+          <t xml:space="preserve">11830
 </t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">497
+          <t xml:space="preserve">487
 </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">1650
 </t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">1718
 </t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">1277
 </t>
         </is>
       </c>
@@ -1448,7 +1467,7 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12241
+          <t xml:space="preserve">2248
 </t>
         </is>
       </c>
@@ -1464,9 +1483,24 @@
 </t>
         </is>
       </c>
-      <c r="X9" s="2" t="n"/>
-      <c r="Y9" s="2" t="n"/>
-      <c r="Z9" s="2" t="n"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1202
+</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1493,25 +1527,26 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">1478
+</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1539,7 +1574,7 @@
 </t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">366
@@ -1548,7 +1583,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -1590,23 +1625,28 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">389
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">11062
+</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">212
 </t>
         </is>
       </c>
-      <c r="Z10" s="2" t="n"/>
       <c r="AA10" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1627,7 +1667,8 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>305</t>
+          <t xml:space="preserve">308
+</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1638,7 +1679,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
@@ -1656,19 +1697,19 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1469
 </t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -1692,7 +1733,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -1710,7 +1751,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -1722,18 +1763,27 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="n"/>
-      <c r="W11" s="2" t="n"/>
+          <t xml:space="preserve">1310
+</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1140
+</t>
+        </is>
+      </c>
       <c r="X11" s="2" t="n"/>
       <c r="Y11" s="2" t="n"/>
       <c r="Z11" s="2" t="n"/>
@@ -1757,19 +1807,19 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10217
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
@@ -1793,7 +1843,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1811,7 +1861,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -1823,25 +1873,24 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3118
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -1853,37 +1902,37 @@
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1840
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1623
+          <t xml:space="preserve">1023
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14170
+          <t xml:space="preserve">470
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -1913,8 +1962,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1929,10 +1977,16 @@
 </t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1114
+</t>
+        </is>
+      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">94
+</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1959,10 +2013,10 @@
 </t>
         </is>
       </c>
-      <c r="N13" s="2" t="n"/>
+      <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8490
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
@@ -1980,7 +2034,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -1998,7 +2052,7 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">440
+          <t xml:space="preserve">4490
 </t>
         </is>
       </c>
@@ -2022,12 +2076,14 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">288
+</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">254
+</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2044,7 +2100,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
+          <t xml:space="preserve">4880
 </t>
         </is>
       </c>
@@ -2056,7 +2112,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -2092,7 +2148,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2104,19 +2160,14 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1220
+</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">495
 </t>
         </is>
       </c>
@@ -2128,19 +2179,19 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">2303
 </t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">045
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">738
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
@@ -2152,7 +2203,7 @@
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
+          <t xml:space="preserve">12360
 </t>
         </is>
       </c>
@@ -2170,19 +2221,19 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -2200,23 +2251,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26521
+          <t xml:space="preserve">5529
 </t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t xml:space="preserve">315
+</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">150
+</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t xml:space="preserve">1231
+</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2257,19 +2311,14 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1104
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1488
+          <t xml:space="preserve">4180
 </t>
         </is>
       </c>
@@ -2281,47 +2330,64 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2310
+</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1145
+</t>
+        </is>
+      </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">380
+</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t xml:space="preserve">271
+</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="Y15" s="2" t="n"/>
-      <c r="Z15" s="2" t="n"/>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>10</t>
@@ -2336,25 +2402,25 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2572
+          <t xml:space="preserve">2377
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82916
+          <t xml:space="preserve">129 16
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">768
 </t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11182
+          <t xml:space="preserve">21182
 </t>
         </is>
       </c>
@@ -2366,19 +2432,19 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
+          <t xml:space="preserve">3973
 </t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">562
+          <t xml:space="preserve">1362
 </t>
         </is>
       </c>
@@ -2388,22 +2454,27 @@
 </t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8809
+</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22125
+          <t xml:space="preserve">2125
 </t>
         </is>
       </c>
@@ -2415,13 +2486,13 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1847
+          <t xml:space="preserve">1547
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">1736
 </t>
         </is>
       </c>
@@ -2433,13 +2504,13 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
@@ -2451,7 +2522,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2463,13 +2534,13 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1458
+          <t xml:space="preserve">11458
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10244
+          <t xml:space="preserve">12244
 </t>
         </is>
       </c>
@@ -2487,19 +2558,20 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23134
+          <t xml:space="preserve">3154
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>244</t>
+          <t xml:space="preserve">134
+</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2510,7 +2582,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
@@ -2522,7 +2594,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -2534,7 +2606,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -2546,19 +2618,19 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2104
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">425
 </t>
         </is>
       </c>
@@ -2588,24 +2660,25 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9274
+          <t xml:space="preserve">376
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9465</t>
+          <t xml:space="preserve">263
+</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
@@ -2623,7 +2696,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -2641,44 +2714,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2321
+          <t xml:space="preserve">2521
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0229
+          <t xml:space="preserve">529
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1124
+</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
-</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -2687,25 +2763,25 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">1375
 </t>
         </is>
       </c>
@@ -2717,7 +2793,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2806
+          <t xml:space="preserve">8291
 </t>
         </is>
       </c>
@@ -2735,36 +2811,46 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">1155
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">404
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">1844
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="Y18" s="2" t="n"/>
-      <c r="Z18" s="2" t="n"/>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>11</t>
@@ -2779,7 +2865,8 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t xml:space="preserve">3264
+</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2812,10 +2899,15 @@
 </t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
@@ -2827,7 +2919,8 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t xml:space="preserve">135
+</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2844,7 +2937,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
+          <t xml:space="preserve">1605
 </t>
         </is>
       </c>
@@ -2862,7 +2955,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -2886,7 +2979,8 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t xml:space="preserve">1269
+</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2897,22 +2991,17 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="Z19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2928
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="n"/>
       <c r="AA19" t="inlineStr">
         <is>
           <t>12</t>
@@ -2927,23 +3016,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>343</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2966,12 +3056,13 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">84
+</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -2989,7 +3080,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -3025,7 +3116,8 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t xml:space="preserve">225
+</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -3036,13 +3128,13 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
@@ -3054,11 +3146,16 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="Z20" s="2" t="n"/>
+          <t xml:space="preserve">320
+</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182
+</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>13</t>
@@ -3085,13 +3182,13 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -3103,7 +3200,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -3121,19 +3218,19 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1757
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -3145,7 +3242,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
@@ -3175,7 +3272,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
@@ -3187,13 +3284,13 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2863
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -3211,8 +3308,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>446</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3229,7 +3325,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9363
+          <t xml:space="preserve">5363
 </t>
         </is>
       </c>
@@ -3271,13 +3367,13 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">020
 </t>
         </is>
       </c>
@@ -3289,22 +3385,17 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">510
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">92
@@ -3331,7 +3422,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
@@ -3343,20 +3434,19 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3397,13 +3487,13 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">735
+          <t xml:space="preserve">725
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11171
+          <t xml:space="preserve">1171
 </t>
         </is>
       </c>
@@ -3439,7 +3529,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">791
 </t>
         </is>
       </c>
@@ -3451,37 +3541,32 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12720
+          <t xml:space="preserve">2720
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
+          <t xml:space="preserve">412
 </t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2544
-</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1544
+</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3686
+          <t xml:space="preserve">366
 </t>
         </is>
       </c>
@@ -3499,19 +3584,19 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1386
+          <t xml:space="preserve">1305
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
+          <t xml:space="preserve">1688
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">1428
 </t>
         </is>
       </c>
@@ -3523,7 +3608,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11224
+          <t xml:space="preserve">1274
 </t>
         </is>
       </c>
@@ -3541,7 +3626,8 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t xml:space="preserve">5095
+</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3552,62 +3638,67 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2234
-</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1022
-</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1174
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2946
 </t>
         </is>
       </c>
@@ -3619,7 +3710,7 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
@@ -3655,7 +3746,8 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
@@ -3690,7 +3782,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4555
+          <t xml:space="preserve">455
 </t>
         </is>
       </c>
@@ -3702,131 +3794,133 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1248
+</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1142
+</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">400
+</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1262
+</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">177
 </t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10248
-</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1142
-</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1109
-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1118
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4010
-</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1140
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8373
-</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1222
-</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1328
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">92
 </t>
         </is>
       </c>
-      <c r="Y25" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11121
+          <t xml:space="preserve">4573
 </t>
         </is>
       </c>
@@ -3856,25 +3950,25 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -3898,13 +3992,13 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -3928,7 +4022,8 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t xml:space="preserve">293
+</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
@@ -3951,13 +4046,13 @@
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
+          <t xml:space="preserve">1334
 </t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -3969,19 +4064,20 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0220
+          <t xml:space="preserve">2220
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">250
+</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3998,13 +4094,13 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">501
+          <t xml:space="preserve">5501
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318 4
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -4034,13 +4130,13 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -4064,19 +4160,19 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -4088,53 +4184,55 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3174
+          <t xml:space="preserve">374
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">148
+</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t xml:space="preserve">1266
+</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1965
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
@@ -4152,7 +4250,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16210
+          <t xml:space="preserve">6210
 </t>
         </is>
       </c>
@@ -4164,25 +4262,25 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1376
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -4194,13 +4292,13 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4218,13 +4316,13 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
@@ -4236,7 +4334,8 @@
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t xml:space="preserve">321
+</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -4247,25 +4346,25 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">5984
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">434
+          <t xml:space="preserve">934
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
@@ -4277,7 +4376,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -4287,7 +4386,11 @@
 </t>
         </is>
       </c>
-      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>19</t>
@@ -4302,7 +4405,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6248
+          <t xml:space="preserve">6249
 </t>
         </is>
       </c>
@@ -4320,7 +4423,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">2383
 </t>
         </is>
       </c>
@@ -4344,12 +4447,13 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81811
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4385,7 +4489,7 @@
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
@@ -4409,7 +4513,7 @@
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">471
+          <t xml:space="preserve">1471
 </t>
         </is>
       </c>
@@ -4421,8 +4525,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
@@ -4439,7 +4542,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230090
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -4457,19 +4560,19 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22819
+          <t xml:space="preserve">27819
 </t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15616
+          <t xml:space="preserve">1616
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7145
+          <t xml:space="preserve">745
 </t>
         </is>
       </c>
@@ -4487,25 +4590,25 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">570
 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">2370
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1358
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -4529,7 +4632,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2223
+          <t xml:space="preserve">2323
 </t>
         </is>
       </c>
@@ -4541,24 +4644,25 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1551
+          <t xml:space="preserve">1531
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -4576,25 +4680,20 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
-</t>
-        </is>
-      </c>
-      <c r="X30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1100
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">668
+</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr"/>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1069
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">1229
+</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4611,7 +4710,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2364
+          <t xml:space="preserve">3364
 </t>
         </is>
       </c>
@@ -4653,16 +4752,11 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1112
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">164
@@ -4671,7 +4765,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110 1
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
@@ -4689,7 +4783,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
@@ -4707,7 +4801,7 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4743,13 +4837,13 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4767,12 +4861,14 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t xml:space="preserve">2086
+</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>238</t>
+          <t xml:space="preserve">338
+</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4793,12 +4889,7 @@
 </t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
+      <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">92
@@ -4813,13 +4904,13 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
@@ -4831,7 +4922,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -4843,7 +4934,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -4867,43 +4958,32 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">474
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11411
+</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1283
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr"/>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>4841</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="X32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -4921,7 +5001,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1225
+          <t xml:space="preserve">4437
 </t>
         </is>
       </c>
@@ -4933,7 +5013,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">1143
 </t>
         </is>
       </c>
@@ -4945,7 +5025,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1167
 </t>
         </is>
       </c>
@@ -4957,7 +5037,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -4975,19 +5055,19 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -5011,7 +5091,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
@@ -5029,7 +5109,7 @@
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1934
+          <t xml:space="preserve">1834
 </t>
         </is>
       </c>
@@ -5041,7 +5121,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -5053,13 +5133,14 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1492
+          <t xml:space="preserve">14209
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">1139
+</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5088,8 +5169,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1056
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -5100,19 +5180,19 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5136,13 +5216,13 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5166,19 +5246,19 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -5190,31 +5270,31 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180 16
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -5232,13 +5312,13 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4399
+          <t xml:space="preserve">4339
 </t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
@@ -5256,13 +5336,13 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1133
 </t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
@@ -5274,14 +5354,13 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>471</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -5298,7 +5377,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5314,16 +5393,21 @@
 </t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">308
+</t>
+        </is>
+      </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1589
 </t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -5335,7 +5419,7 @@
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">334
 </t>
         </is>
       </c>
@@ -5359,11 +5443,16 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21215
-</t>
-        </is>
-      </c>
-      <c r="Z35" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>24</t>
@@ -5384,35 +5473,45 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">1048
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
@@ -5434,7 +5533,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
@@ -5458,19 +5557,19 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -5482,25 +5581,25 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1806
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11860
+          <t xml:space="preserve">1466
 </t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
@@ -5524,7 +5623,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118106
+          <t xml:space="preserve">1316
 </t>
         </is>
       </c>
@@ -5536,7 +5635,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
@@ -5548,7 +5647,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">338
+          <t xml:space="preserve">558
 </t>
         </is>
       </c>
@@ -5560,13 +5659,13 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">361
 </t>
         </is>
       </c>
@@ -5578,31 +5677,31 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">032
+          <t xml:space="preserve">1532
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">447
 </t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12402
+          <t xml:space="preserve">24092
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">893
+          <t xml:space="preserve">3595
 </t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133 5
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -5620,7 +5719,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11510
+          <t xml:space="preserve">1716
 </t>
         </is>
       </c>
@@ -5632,31 +5731,26 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">11411
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
-        </is>
-      </c>
-      <c r="X37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">498
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr"/>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11812
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
@@ -5674,19 +5768,19 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4422
+          <t xml:space="preserve">4433
 </t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2303
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
@@ -5698,13 +5792,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -5716,19 +5810,14 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -5740,37 +5829,37 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -5782,13 +5871,13 @@
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">1269
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
@@ -5830,30 +5919,31 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9146
+          <t xml:space="preserve">59146
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t xml:space="preserve">292
+</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11866
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108110
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -5865,37 +5955,38 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">11580
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">9
+</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -5930,13 +6021,13 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0294
+          <t xml:space="preserve">1294
 </t>
         </is>
       </c>
@@ -5954,7 +6045,7 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -5966,7 +6057,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -5984,12 +6075,13 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>6414</t>
+          <t xml:space="preserve">6171
+</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">907
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -6019,7 +6111,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6031,13 +6123,13 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -6049,13 +6141,13 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
@@ -6073,13 +6165,13 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -6091,13 +6183,13 @@
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">842
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">12680
 </t>
         </is>
       </c>
@@ -6109,19 +6201,20 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">3180
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t xml:space="preserve">2236
+</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6150,25 +6243,24 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1530
 </t>
         </is>
       </c>
@@ -6198,19 +6290,19 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
@@ -6240,13 +6332,13 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">2326
 </t>
         </is>
       </c>
@@ -6258,20 +6350,26 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1016
-</t>
-        </is>
-      </c>
-      <c r="Y41" s="2" t="inlineStr"/>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1289
+</t>
+        </is>
+      </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">264
+</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6294,7 +6392,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">392
 </t>
         </is>
       </c>
@@ -6306,13 +6404,13 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">1233
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -6330,7 +6428,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -6348,26 +6446,25 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -6390,7 +6487,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">1287
 </t>
         </is>
       </c>
@@ -6402,13 +6499,13 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -6420,11 +6517,16 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="2" t="n"/>
+          <t xml:space="preserve">13920
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>29</t>
@@ -6439,13 +6541,13 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5340
+          <t xml:space="preserve">2340
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -6463,13 +6565,13 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
@@ -6487,7 +6589,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -6505,7 +6607,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -6517,7 +6619,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -6541,13 +6643,13 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">2314
 </t>
         </is>
       </c>
@@ -6559,7 +6661,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -6577,7 +6679,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -6595,7 +6697,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2280
+          <t xml:space="preserve">2580
 </t>
         </is>
       </c>
@@ -6613,7 +6715,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
@@ -6643,7 +6745,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">092
 </t>
         </is>
       </c>
@@ -6655,24 +6757,25 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">6440
 </t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
@@ -6684,7 +6787,7 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -6696,13 +6799,13 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3228
+          <t xml:space="preserve">2328
 </t>
         </is>
       </c>
@@ -6720,16 +6823,22 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">12279
+</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2908
+</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1124
+</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>31</t>
@@ -6744,43 +6853,42 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18011
+          <t xml:space="preserve">23122
 </t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851
+          <t xml:space="preserve">1887
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11221
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">9108
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">71949
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7211
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
@@ -6792,89 +6900,84 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12818
+          <t xml:space="preserve">1019
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">12029
 </t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12265
+          <t xml:space="preserve">2265
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">29084
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1700
-</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0815
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1780
+</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
-</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1369
+</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1826
+</t>
+        </is>
+      </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1442
+          <t xml:space="preserve">1462
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">2862
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 1
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12229
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1647
+</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr"/>
       <c r="Z45" s="2" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
@@ -6890,30 +6993,31 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t xml:space="preserve">5518
+</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">406
+          <t xml:space="preserve">4706
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -6925,7 +7029,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -6935,12 +7039,7 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">168
@@ -6949,19 +7048,19 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">494
+          <t xml:space="preserve">1494
 </t>
         </is>
       </c>
@@ -6979,13 +7078,13 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">1390
 </t>
         </is>
       </c>
@@ -6997,13 +7096,13 @@
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">23908
 </t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">2848
 </t>
         </is>
       </c>
@@ -7015,19 +7114,19 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/501/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/501/Top_Excel_with_OCR_Results.xlsx
@@ -626,110 +626,92 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5698
-</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
+          <t>335</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">355
-</t>
+          <t>355</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="U4" s="2" t="n"/>
@@ -752,141 +734,118 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1360
-</t>
+          <t>360</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1468
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -903,141 +862,118 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5048
-</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">339
-</t>
+          <t>339</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20239
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1400
-</t>
+          <t>400</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
-</t>
+          <t>327</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
-</t>
+          <t>410</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2302
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1054,8 +990,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5836
-</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1065,134 +1000,112 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">347
-</t>
+          <t>347</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">424
-</t>
+          <t>424</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1209,135 +1122,113 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4851
-</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">362
-</t>
+          <t>362</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>517</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">422
-</t>
+          <t>422</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1359,146 +1250,122 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26361
-</t>
+          <t>26560</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1697
-</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
-</t>
+          <t>533</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11134
-</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
-</t>
+          <t>391</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
-</t>
+          <t>442</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
-</t>
+          <t>684</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1671
-</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11830
-</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">487
-</t>
+          <t>497</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650
-</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
-</t>
+          <t>718</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2248
-</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
-</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1696
-</t>
+          <t>696</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1515,136 +1382,114 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312
-</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>339</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1478
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
-</t>
+          <t>448</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">389
-</t>
+          <t>389</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11062
-</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,104 +1506,87 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1768,20 +1596,17 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X11" s="2" t="n"/>
@@ -1801,8 +1626,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2067
-</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1813,74 +1637,62 @@
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
-</t>
+          <t>530</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
@@ -1890,50 +1702,42 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
-</t>
+          <t>392</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1023
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1950,14 +1754,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6013
-</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">343
-</t>
+          <t>343</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1967,123 +1769,103 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4490
-</t>
+          <t>440</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2100,141 +1882,118 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880
-</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
-</t>
+          <t>495</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12360
-</t>
+          <t>360</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2251,141 +2010,118 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5529
-</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
-</t>
+          <t>380</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2402,146 +2138,122 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2377
-</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129 16
-</t>
+          <t>159 6</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21182
-</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>828</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
-</t>
+          <t>618</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3973
-</t>
+          <t>353</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1362
-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8809
-</t>
+          <t>899</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125
-</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
-</t>
+          <t>622</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1547
-</t>
+          <t>1547</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1736
-</t>
+          <t>736</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
-</t>
+          <t>364</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
-</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1313
-</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>725</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">483
-</t>
+          <t>483</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11458
-</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12244
-</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2558,146 +2270,122 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
-</t>
+          <t>425</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">376
-</t>
+          <t>376</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2714,141 +2402,118 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2521
-</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1375
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8291
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1844
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2865,140 +2530,117 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264
-</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
-</t>
+          <t>605</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">414
-</t>
+          <t>414</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Z19" s="2" t="n"/>
@@ -3026,134 +2668,112 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3170,140 +2790,117 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0422
-</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -3325,123 +2922,103 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363
-</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">020
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390
-</t>
+          <t>390</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
@@ -3451,14 +3028,12 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3475,141 +3050,118 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25175
-</t>
+          <t>25475</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1603
-</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
-</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
-</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
-</t>
+          <t>868</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>572</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">791
-</t>
+          <t>791</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
-</t>
+          <t>503</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2720
-</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
-</t>
+          <t>413</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1544
-</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
+          <t>829</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1872
-</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1305
-</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1688
-</t>
+          <t>688</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>428</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
-</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
-</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3626,146 +3178,122 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5095
-</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2946
-</t>
+          <t>546</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3782,146 +3310,122 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">455
-</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
-</t>
+          <t>400</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4573
-</t>
+          <t>453</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3938,146 +3442,122 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304
-</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4094,146 +3574,122 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5501
-</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4250,140 +3706,117 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6210
-</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5984
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">934
-</t>
+          <t>434</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -4405,122 +3838,102 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6249
-</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2383
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
-</t>
+          <t>413</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
+          <t>335</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1471
-</t>
+          <t>471</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4530,20 +3943,17 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4560,128 +3970,107 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27819
-</t>
+          <t>27819</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616
-</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
-</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
-</t>
+          <t>871</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">570
-</t>
+          <t>570</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2370
-</t>
+          <t>370</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1358
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2323
-</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>517</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
-</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>709</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>726</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1941
-</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
-</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr"/>
@@ -4692,8 +4081,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4710,141 +4098,118 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3364
-</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">465
-</t>
+          <t>465</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">388
-</t>
+          <t>388</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4861,118 +4226,99 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086
-</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">338
-</t>
+          <t>338</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
-</t>
+          <t>390</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">336
-</t>
+          <t>336</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11411
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr"/>
@@ -4983,8 +4329,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5001,146 +4346,122 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4437
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
-</t>
+          <t>410</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14209
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5157,14 +4478,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3866
-</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -5174,128 +4493,107 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>522</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5312,50 +4610,42 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339
-</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -5365,92 +4655,77 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1589
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5467,8 +4742,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3413
-</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -5478,129 +4752,108 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1048
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
-</t>
+          <t>540</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
-</t>
+          <t>348</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1806
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1466
-</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5617,141 +4870,118 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22166
-</t>
+          <t>22166</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1316
-</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
-</t>
+          <t>689</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
-</t>
+          <t>827</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
-</t>
+          <t>558</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>839</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1532
-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">447
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24092
-</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3595
-</t>
+          <t>593</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
-</t>
+          <t>726</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1478
-</t>
+          <t>479</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1716
-</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1340
-</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11411
-</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>070</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr"/>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
-</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5768,141 +4998,118 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433
-</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5919,146 +5126,122 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59146
-</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11580
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1294
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
-</t>
+          <t>364</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6075,146 +5258,122 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
-</t>
+          <t>510</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
-</t>
+          <t>342</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12680
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3180
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6231,14 +5390,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5875
-</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -6248,128 +5405,107 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1530
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6386,80 +5522,67 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4811
-</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">392
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -6469,62 +5592,52 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13920
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6541,146 +5654,122 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2340
-</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>315</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6697,146 +5786,122 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580
-</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">092
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440
-</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12279
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2908
-</t>
+          <t>508</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6853,14 +5918,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23122
-</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
-</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -6870,111 +5933,93 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9108
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71949
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>350</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">523
-</t>
+          <t>523</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
-</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12029
-</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2265
-</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29084
-</t>
+          <t>584</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1780
-</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr"/>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1369
-</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1826
-</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1462
-</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2862
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1647
-</t>
+          <t>547</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr"/>
@@ -6993,141 +6038,122 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518
-</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4706
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
-</t>
+          <t>494</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1390
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23908
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2848
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">

--- a/results/05_transient_transcription_output/501/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/501/Top_Excel_with_OCR_Results.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>124</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -1045,12 +1045,12 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>350</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>317</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>333</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>262</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>268</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>362</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>41</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>125</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>76</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>375</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>404</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>67</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>96</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr"/>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>222</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>272</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>011</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
@@ -3457,12 +3457,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>135</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>320</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>194</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>62</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>27819</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>358</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>318</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>62</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>273</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>014</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr"/>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>322</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4588,12 +4588,12 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>300</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>340</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>358</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>393</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>070</t>
+          <t>670</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr"/>
@@ -5036,7 +5036,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
           <t>168</t>
@@ -5049,7 +5053,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>92</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -5079,7 +5083,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>303</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -5186,7 +5190,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>310</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5258,7 +5262,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5313,7 +5317,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -5445,7 +5449,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -5622,12 +5626,12 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5694,7 +5698,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -5754,7 +5758,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
@@ -5826,7 +5830,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -5841,12 +5845,12 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>440</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5871,7 +5875,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>193</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5918,7 +5922,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>33122</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5933,7 +5937,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>137</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5953,7 +5957,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>323</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -5968,12 +5972,12 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>270</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -6014,12 +6018,12 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>863</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr"/>
@@ -6043,7 +6047,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -6058,7 +6062,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>153</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -6093,7 +6097,7 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -6138,7 +6142,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>124</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
@@ -6148,7 +6152,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>311</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">

--- a/results/05_transient_transcription_output/501/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/501/Top_Excel_with_OCR_Results.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>123</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -1045,12 +1045,12 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1178,7 +1178,7 @@
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>262</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>517</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1938,7 +1938,7 @@
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>480</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>562</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>725</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>554</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>175</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr"/>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>785</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>690</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>572</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>099</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
@@ -3457,12 +3457,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3497,12 +3497,12 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>320</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>520</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>104</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>94</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>434</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>27819</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>558</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>194</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>68</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>611</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>014</t>
+          <t>004</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr"/>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>437</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>422</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>108</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>332</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>341</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>22166</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>558</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>070</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr"/>
@@ -5036,11 +5036,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
           <t>168</t>
@@ -5053,7 +5049,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>97</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -5150,7 +5146,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -5185,7 +5181,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -5317,7 +5313,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -5347,7 +5343,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>195</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -5449,7 +5445,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -5499,7 +5495,7 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5626,12 +5622,12 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>118</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5713,7 +5709,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -5790,7 +5786,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>580</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5845,7 +5841,7 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -5875,7 +5871,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>198</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5895,7 +5891,7 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>109</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5922,7 +5918,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>33122</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5947,7 +5943,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>719</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -5957,7 +5953,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>523</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -5972,12 +5968,12 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>650</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>578</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -6008,7 +6004,7 @@
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
@@ -6023,7 +6019,7 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>647</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr"/>
@@ -6082,7 +6078,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -6097,7 +6093,7 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -6142,7 +6138,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
@@ -6152,7 +6148,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>211</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
